--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="152">
   <si>
     <t>##var</t>
   </si>
@@ -55,6 +55,9 @@
     <t>PrefabResourcePath</t>
   </si>
   <si>
+    <t>TestPrefabResourcePath</t>
+  </si>
+  <si>
     <t>Comment</t>
   </si>
   <si>
@@ -106,6 +109,9 @@
     <t>预制体资源路径</t>
   </si>
   <si>
+    <t>测试预制体资源路径</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -121,6 +127,9 @@
     <t>Arts/Prefabs/Animals/Animal_Small_101</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Small_101</t>
+  </si>
+  <si>
     <t>示例</t>
   </si>
   <si>
@@ -130,66 +139,99 @@
     <t>Arts/Prefabs/Animals/Animal_Small_102</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Small_102</t>
+  </si>
+  <si>
     <t>SmallAnimal3</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Small_103</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Small_103</t>
+  </si>
+  <si>
     <t>SmallAnimal4</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Small_104</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Small_104</t>
+  </si>
+  <si>
     <t>SmallAnimal5</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Small_105</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Small_105</t>
+  </si>
+  <si>
     <t>SmallAnimal6</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Small_106</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Small_106</t>
+  </si>
+  <si>
     <t>SmallAnimal7</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Small_107</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Small_107</t>
+  </si>
+  <si>
     <t>SmallAnimal8</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Small_108</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Small_108</t>
+  </si>
+  <si>
     <t>SmallAnimal9</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Small_109</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Small_109</t>
+  </si>
+  <si>
     <t>SmallAnimal10</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Small_110</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Small_110</t>
+  </si>
+  <si>
     <t>SmallAnimal11</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Small_111</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Small_111</t>
+  </si>
+  <si>
     <t>SmallAnimal12</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Small_112</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Small_112</t>
+  </si>
+  <si>
     <t>MediumAnimal1</t>
   </si>
   <si>
@@ -202,108 +244,162 @@
     <t>Arts/Prefabs/Animals/Animal_Medium_201</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Medium_201</t>
+  </si>
+  <si>
     <t>MediumAnimal2</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Medium_202</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Medium_202</t>
+  </si>
+  <si>
     <t>MediumAnimal3</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Medium_203</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Medium_203</t>
+  </si>
+  <si>
     <t>MediumAnimal4</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Medium_204</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Medium_204</t>
+  </si>
+  <si>
     <t>MediumAnimal5</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Medium_205</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Medium_205</t>
+  </si>
+  <si>
     <t>MediumAnimal6</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Medium_206</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Medium_206</t>
+  </si>
+  <si>
     <t>MediumAnimal7</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Medium_207</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Medium_207</t>
+  </si>
+  <si>
     <t>MediumAnimal8</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Medium_208</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Medium_208</t>
+  </si>
+  <si>
     <t>MediumAnimal9</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Medium_209</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Medium_209</t>
+  </si>
+  <si>
     <t>MediumAnimal10</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Medium_210</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Medium_210</t>
+  </si>
+  <si>
     <t>MediumAnimal11</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Medium_211</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Medium_211</t>
+  </si>
+  <si>
     <t>MediumAnimal12</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Medium_212</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Medium_212</t>
+  </si>
+  <si>
     <t>MediumAnimal13</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Medium_213</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Medium_213</t>
+  </si>
+  <si>
     <t>MediumAnimal14</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Medium_214</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Medium_214</t>
+  </si>
+  <si>
     <t>MediumAnimal15</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Medium_215</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Medium_215</t>
+  </si>
+  <si>
     <t>MediumAnimal16</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Medium_216</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Medium_216</t>
+  </si>
+  <si>
     <t>MediumAnimal17</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Medium_217</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Medium_217</t>
+  </si>
+  <si>
     <t>MediumAnimal18</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Medium_218</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Medium_218</t>
+  </si>
+  <si>
     <t>LargeAnimalC1</t>
   </si>
   <si>
@@ -316,36 +412,54 @@
     <t>Arts/Prefabs/Animals/Animal_Large_301</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Large_301</t>
+  </si>
+  <si>
     <t>LargeAnimalC2</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Large_302</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Large_302</t>
+  </si>
+  <si>
     <t>LargeAnimalC3</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Large_303</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Large_303</t>
+  </si>
+  <si>
     <t>LargeAnimalC4</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Large_304</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Large_304</t>
+  </si>
+  <si>
     <t>LargeAnimalC5</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Large_305</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Large_305</t>
+  </si>
+  <si>
     <t>LargeAnimalC6</t>
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Large_306</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Large_306</t>
+  </si>
+  <si>
     <t>弹药怪</t>
   </si>
   <si>
@@ -358,6 +472,9 @@
     <t>Arts/Prefabs/Animals/Animal_Special_401</t>
   </si>
   <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Special_401</t>
+  </si>
+  <si>
     <t>金币怪</t>
   </si>
   <si>
@@ -365,6 +482,9 @@
   </si>
   <si>
     <t>Arts/Prefabs/Animals/Animal_Special_402</t>
+  </si>
+  <si>
+    <t>Arts/Prefabs/Animals/TestAnimal_Special_402</t>
   </si>
 </sst>
 </file>
@@ -1334,15 +1454,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="6" width="28.625" customWidth="1"/>
     <col min="7" max="7" width="62.7833333333333" customWidth="1"/>
-    <col min="8" max="9" width="28.625" customWidth="1"/>
+    <col min="8" max="9" width="48.625" customWidth="1"/>
+    <col min="10" max="10" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:9">
+    <row r="1" ht="28" customHeight="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1370,104 +1491,116 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" ht="28" customHeight="1" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:9">
+        <v>12</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:9">
+        <v>17</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:9">
+        <v>26</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1" spans="1:10">
       <c r="A5" s="3"/>
       <c r="B5" s="3">
         <v>101</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E5" s="3">
         <v>30</v>
@@ -1476,25 +1609,28 @@
         <v>8</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:10">
       <c r="A6" s="3"/>
       <c r="B6" s="3">
         <v>102</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E6" s="3">
         <v>30</v>
@@ -1503,25 +1639,28 @@
         <v>8</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:9">
+        <v>36</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:10">
       <c r="A7" s="3"/>
       <c r="B7" s="3">
         <v>103</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E7" s="3">
         <v>30</v>
@@ -1530,25 +1669,28 @@
         <v>8</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:9">
+        <v>39</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1" spans="1:10">
       <c r="A8" s="3"/>
       <c r="B8" s="3">
         <v>104</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E8" s="3">
         <v>30</v>
@@ -1557,25 +1699,28 @@
         <v>8</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:9">
+        <v>42</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1" spans="1:10">
       <c r="A9" s="3"/>
       <c r="B9" s="3">
         <v>105</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E9" s="3">
         <v>30</v>
@@ -1584,25 +1729,28 @@
         <v>8</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:9">
+        <v>45</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:10">
       <c r="A10" s="3"/>
       <c r="B10" s="3">
         <v>106</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E10" s="3">
         <v>30</v>
@@ -1611,25 +1759,28 @@
         <v>8</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:9">
+        <v>48</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:10">
       <c r="A11" s="3"/>
       <c r="B11" s="3">
         <v>107</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E11" s="3">
         <v>30</v>
@@ -1638,25 +1789,28 @@
         <v>8</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:9">
+        <v>51</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:10">
       <c r="A12" s="3"/>
       <c r="B12" s="3">
         <v>108</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E12" s="3">
         <v>30</v>
@@ -1665,25 +1819,28 @@
         <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:9">
+        <v>54</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:10">
       <c r="A13" s="3"/>
       <c r="B13" s="3">
         <v>109</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E13" s="3">
         <v>30</v>
@@ -1692,25 +1849,28 @@
         <v>8</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="1:9">
+        <v>57</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1" spans="1:10">
       <c r="A14" s="3"/>
       <c r="B14" s="3">
         <v>110</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E14" s="3">
         <v>30</v>
@@ -1719,25 +1879,28 @@
         <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:9">
+        <v>60</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1" spans="1:10">
       <c r="A15" s="3"/>
       <c r="B15" s="3">
         <v>111</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E15" s="3">
         <v>30</v>
@@ -1746,25 +1909,28 @@
         <v>8</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1" spans="1:9">
+        <v>63</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:10">
       <c r="A16" s="3"/>
       <c r="B16" s="3">
         <v>112</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E16" s="3">
         <v>30</v>
@@ -1773,25 +1939,28 @@
         <v>8</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1" spans="1:9">
+        <v>66</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="1:10">
       <c r="A17" s="3"/>
       <c r="B17" s="3">
         <v>201</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E17" s="3">
         <v>60</v>
@@ -1800,25 +1969,28 @@
         <v>6</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1" spans="1:9">
+        <v>71</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1" spans="1:10">
       <c r="A18" s="3"/>
       <c r="B18" s="3">
         <v>202</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E18" s="3">
         <v>60</v>
@@ -1827,25 +1999,28 @@
         <v>6</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:9">
+        <v>74</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1" spans="1:10">
       <c r="A19" s="3"/>
       <c r="B19" s="3">
         <v>203</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E19" s="3">
         <v>60</v>
@@ -1854,25 +2029,28 @@
         <v>6</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="1:9">
+        <v>77</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1" spans="1:10">
       <c r="A20" s="3"/>
       <c r="B20" s="3">
         <v>204</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E20" s="3">
         <v>60</v>
@@ -1881,25 +2059,28 @@
         <v>6</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1" spans="1:9">
+        <v>80</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1" spans="1:10">
       <c r="A21" s="3"/>
       <c r="B21" s="3">
         <v>205</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E21" s="3">
         <v>60</v>
@@ -1908,25 +2089,28 @@
         <v>6</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1" spans="1:9">
+        <v>83</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1" spans="1:10">
       <c r="A22" s="3"/>
       <c r="B22" s="3">
         <v>206</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E22" s="3">
         <v>60</v>
@@ -1935,25 +2119,28 @@
         <v>6</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1" spans="1:9">
+        <v>86</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:10">
       <c r="A23" s="3"/>
       <c r="B23" s="3">
         <v>207</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E23" s="3">
         <v>60</v>
@@ -1962,25 +2149,28 @@
         <v>6</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1" spans="1:9">
+        <v>89</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1" spans="1:10">
       <c r="A24" s="3"/>
       <c r="B24" s="3">
         <v>208</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E24" s="3">
         <v>60</v>
@@ -1989,25 +2179,28 @@
         <v>6</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1" spans="1:9">
+        <v>92</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1" spans="1:10">
       <c r="A25" s="3"/>
       <c r="B25" s="3">
         <v>209</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E25" s="3">
         <v>60</v>
@@ -2016,25 +2209,28 @@
         <v>6</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1" spans="1:9">
+        <v>95</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1" spans="1:10">
       <c r="A26" s="3"/>
       <c r="B26" s="3">
         <v>210</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E26" s="3">
         <v>60</v>
@@ -2043,25 +2239,28 @@
         <v>6</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1" spans="1:9">
+        <v>98</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1" spans="1:10">
       <c r="A27" s="3"/>
       <c r="B27" s="3">
         <v>211</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E27" s="3">
         <v>60</v>
@@ -2070,25 +2269,28 @@
         <v>6</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1" spans="1:9">
+        <v>101</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1" spans="1:10">
       <c r="A28" s="3"/>
       <c r="B28" s="3">
         <v>212</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E28" s="3">
         <v>60</v>
@@ -2097,25 +2299,28 @@
         <v>6</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1" spans="1:9">
+        <v>104</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1" spans="1:10">
       <c r="A29" s="3"/>
       <c r="B29" s="3">
         <v>213</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E29" s="3">
         <v>60</v>
@@ -2124,25 +2329,28 @@
         <v>6</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1" spans="1:9">
+        <v>107</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1" spans="1:10">
       <c r="A30" s="3"/>
       <c r="B30" s="3">
         <v>214</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E30" s="3">
         <v>60</v>
@@ -2151,25 +2359,28 @@
         <v>6</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1" spans="1:9">
+        <v>110</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1" spans="1:10">
       <c r="A31" s="3"/>
       <c r="B31" s="3">
         <v>215</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E31" s="3">
         <v>60</v>
@@ -2178,25 +2389,28 @@
         <v>6</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1" spans="1:9">
+        <v>113</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1" spans="1:10">
       <c r="A32" s="3"/>
       <c r="B32" s="3">
         <v>216</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E32" s="3">
         <v>60</v>
@@ -2205,25 +2419,28 @@
         <v>6</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1" spans="1:9">
+        <v>116</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1" spans="1:10">
       <c r="A33" s="3"/>
       <c r="B33" s="3">
         <v>217</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E33" s="3">
         <v>60</v>
@@ -2232,25 +2449,28 @@
         <v>6</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1" spans="1:9">
+        <v>119</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1" spans="1:10">
       <c r="A34" s="3"/>
       <c r="B34" s="3">
         <v>218</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E34" s="3">
         <v>60</v>
@@ -2259,25 +2479,28 @@
         <v>6</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1" spans="1:9">
+        <v>122</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1" spans="1:10">
       <c r="A35" s="3"/>
       <c r="B35" s="3">
         <v>301</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="E35" s="3">
         <v>120</v>
@@ -2286,25 +2509,28 @@
         <v>4</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1" spans="1:9">
+        <v>127</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1" spans="1:10">
       <c r="A36" s="3"/>
       <c r="B36" s="3">
         <v>302</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="E36" s="3">
         <v>120</v>
@@ -2313,25 +2539,28 @@
         <v>4</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1" spans="1:9">
+        <v>130</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1" spans="1:10">
       <c r="A37" s="3"/>
       <c r="B37" s="3">
         <v>303</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>97</v>
+        <v>131</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="E37" s="3">
         <v>120</v>
@@ -2340,25 +2569,28 @@
         <v>4</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1" spans="1:9">
+        <v>133</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1" spans="1:10">
       <c r="A38" s="3"/>
       <c r="B38" s="3">
         <v>304</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="E38" s="3">
         <v>120</v>
@@ -2367,25 +2599,28 @@
         <v>4</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1" spans="1:9">
+        <v>136</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1" spans="1:10">
       <c r="A39" s="3"/>
       <c r="B39" s="3">
         <v>305</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="E39" s="3">
         <v>120</v>
@@ -2394,25 +2629,28 @@
         <v>4</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1" spans="1:9">
+        <v>139</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1" spans="1:10">
       <c r="A40" s="3"/>
       <c r="B40" s="3">
         <v>306</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="E40" s="3">
         <v>120</v>
@@ -2421,25 +2659,28 @@
         <v>4</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1" spans="1:9">
+        <v>142</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1" spans="1:10">
       <c r="A41" s="3"/>
       <c r="B41" s="3">
         <v>401</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="E41" s="3">
         <v>60</v>
@@ -2448,25 +2689,28 @@
         <v>6</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1" spans="1:9">
+        <v>147</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1" spans="1:10">
       <c r="A42" s="3"/>
       <c r="B42" s="3">
         <v>402</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="E42" s="3">
         <v>120</v>
@@ -2475,13 +2719,16 @@
         <v>6</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>30</v>
+        <v>151</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -115,7 +115,7 @@
     <t>备注</t>
   </si>
   <si>
-    <t>SmallAnimal1</t>
+    <t>兔子</t>
   </si>
   <si>
     <t>Small</t>
@@ -124,115 +124,13 @@
     <t>Meat:1|Bullet:0|Coin:0|Energy:1</t>
   </si>
   <si>
-    <t>Arts/Prefabs/Animals/Animal_Small_101</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Small_101</t>
-  </si>
-  <si>
-    <t>示例</t>
-  </si>
-  <si>
-    <t>SmallAnimal2</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Small_102</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Small_102</t>
-  </si>
-  <si>
-    <t>SmallAnimal3</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Small_103</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Small_103</t>
-  </si>
-  <si>
-    <t>SmallAnimal4</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Small_104</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Small_104</t>
-  </si>
-  <si>
-    <t>SmallAnimal5</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Small_105</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Small_105</t>
-  </si>
-  <si>
-    <t>SmallAnimal6</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Small_106</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Small_106</t>
-  </si>
-  <si>
-    <t>SmallAnimal7</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Small_107</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Small_107</t>
-  </si>
-  <si>
-    <t>SmallAnimal8</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Small_108</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Small_108</t>
-  </si>
-  <si>
-    <t>SmallAnimal9</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Small_109</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Small_109</t>
-  </si>
-  <si>
-    <t>SmallAnimal10</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Small_110</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Small_110</t>
-  </si>
-  <si>
-    <t>SmallAnimal11</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Small_111</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Small_111</t>
-  </si>
-  <si>
-    <t>SmallAnimal12</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Small_112</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Small_112</t>
-  </si>
-  <si>
-    <t>MediumAnimal1</t>
+    <t>Arts/Animals/Prefabs/Animal_Forest_Small_Rabbit</t>
+  </si>
+  <si>
+    <t>Arts/Animals/Prefabs/Animal_Forest_Small_Rabbit_Test</t>
+  </si>
+  <si>
+    <t>/</t>
   </si>
   <si>
     <t>Medium</t>
@@ -241,225 +139,12 @@
     <t>Meat:5|Bullet:0|Coin:0|Energy:2</t>
   </si>
   <si>
-    <t>Arts/Prefabs/Animals/Animal_Medium_201</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Medium_201</t>
-  </si>
-  <si>
-    <t>MediumAnimal2</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Medium_202</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Medium_202</t>
-  </si>
-  <si>
-    <t>MediumAnimal3</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Medium_203</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Medium_203</t>
-  </si>
-  <si>
-    <t>MediumAnimal4</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Medium_204</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Medium_204</t>
-  </si>
-  <si>
-    <t>MediumAnimal5</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Medium_205</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Medium_205</t>
-  </si>
-  <si>
-    <t>MediumAnimal6</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Medium_206</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Medium_206</t>
-  </si>
-  <si>
-    <t>MediumAnimal7</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Medium_207</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Medium_207</t>
-  </si>
-  <si>
-    <t>MediumAnimal8</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Medium_208</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Medium_208</t>
-  </si>
-  <si>
-    <t>MediumAnimal9</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Medium_209</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Medium_209</t>
-  </si>
-  <si>
-    <t>MediumAnimal10</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Medium_210</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Medium_210</t>
-  </si>
-  <si>
-    <t>MediumAnimal11</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Medium_211</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Medium_211</t>
-  </si>
-  <si>
-    <t>MediumAnimal12</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Medium_212</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Medium_212</t>
-  </si>
-  <si>
-    <t>MediumAnimal13</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Medium_213</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Medium_213</t>
-  </si>
-  <si>
-    <t>MediumAnimal14</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Medium_214</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Medium_214</t>
-  </si>
-  <si>
-    <t>MediumAnimal15</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Medium_215</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Medium_215</t>
-  </si>
-  <si>
-    <t>MediumAnimal16</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Medium_216</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Medium_216</t>
-  </si>
-  <si>
-    <t>MediumAnimal17</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Medium_217</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Medium_217</t>
-  </si>
-  <si>
-    <t>MediumAnimal18</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Medium_218</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Medium_218</t>
-  </si>
-  <si>
-    <t>LargeAnimalC1</t>
-  </si>
-  <si>
     <t>Large</t>
   </si>
   <si>
     <t>Meat:10|Bullet:0|Coin:0|Energy:5</t>
   </si>
   <si>
-    <t>Arts/Prefabs/Animals/Animal_Large_301</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Large_301</t>
-  </si>
-  <si>
-    <t>LargeAnimalC2</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Large_302</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Large_302</t>
-  </si>
-  <si>
-    <t>LargeAnimalC3</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Large_303</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Large_303</t>
-  </si>
-  <si>
-    <t>LargeAnimalC4</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Large_304</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Large_304</t>
-  </si>
-  <si>
-    <t>LargeAnimalC5</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Large_305</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Large_305</t>
-  </si>
-  <si>
-    <t>LargeAnimalC6</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Large_306</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Large_306</t>
-  </si>
-  <si>
     <t>弹药怪</t>
   </si>
   <si>
@@ -469,22 +154,10 @@
     <t>Meat:5|Bullet:1|Coin:0|Energy:5</t>
   </si>
   <si>
-    <t>Arts/Prefabs/Animals/Animal_Special_401</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Special_401</t>
-  </si>
-  <si>
     <t>金币怪</t>
   </si>
   <si>
     <t>Meat:10|Bullet:0|Coin:10|Energy:5</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/Animal_Special_402</t>
-  </si>
-  <si>
-    <t>Arts/Prefabs/Animals/TestAnimal_Special_402</t>
   </si>
 </sst>
 </file>
@@ -1606,7 +1279,7 @@
         <v>30</v>
       </c>
       <c r="F5" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>30</v>
@@ -1627,7 +1300,7 @@
         <v>102</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>29</v>
@@ -1636,16 +1309,16 @@
         <v>30</v>
       </c>
       <c r="F6" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>30</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>33</v>
@@ -1657,7 +1330,7 @@
         <v>103</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>29</v>
@@ -1666,16 +1339,16 @@
         <v>30</v>
       </c>
       <c r="F7" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>30</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>33</v>
@@ -1687,7 +1360,7 @@
         <v>104</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>29</v>
@@ -1696,16 +1369,16 @@
         <v>30</v>
       </c>
       <c r="F8" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>30</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>33</v>
@@ -1717,7 +1390,7 @@
         <v>105</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>29</v>
@@ -1726,16 +1399,16 @@
         <v>30</v>
       </c>
       <c r="F9" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>30</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>33</v>
@@ -1747,7 +1420,7 @@
         <v>106</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>29</v>
@@ -1756,16 +1429,16 @@
         <v>30</v>
       </c>
       <c r="F10" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>30</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>33</v>
@@ -1777,7 +1450,7 @@
         <v>107</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>29</v>
@@ -1786,16 +1459,16 @@
         <v>30</v>
       </c>
       <c r="F11" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>30</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>33</v>
@@ -1807,7 +1480,7 @@
         <v>108</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>29</v>
@@ -1816,16 +1489,16 @@
         <v>30</v>
       </c>
       <c r="F12" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>30</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>33</v>
@@ -1837,7 +1510,7 @@
         <v>109</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>29</v>
@@ -1846,16 +1519,16 @@
         <v>30</v>
       </c>
       <c r="F13" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>30</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>33</v>
@@ -1867,7 +1540,7 @@
         <v>110</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>29</v>
@@ -1876,16 +1549,16 @@
         <v>30</v>
       </c>
       <c r="F14" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>30</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>33</v>
@@ -1897,7 +1570,7 @@
         <v>111</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>29</v>
@@ -1906,16 +1579,16 @@
         <v>30</v>
       </c>
       <c r="F15" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>33</v>
@@ -1927,7 +1600,7 @@
         <v>112</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>29</v>
@@ -1936,16 +1609,16 @@
         <v>30</v>
       </c>
       <c r="F16" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>33</v>
@@ -1957,25 +1630,25 @@
         <v>201</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="E17" s="3">
         <v>60</v>
       </c>
       <c r="F17" s="3">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>33</v>
@@ -1987,25 +1660,25 @@
         <v>202</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="E18" s="3">
         <v>60</v>
       </c>
       <c r="F18" s="3">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>33</v>
@@ -2017,25 +1690,25 @@
         <v>203</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="E19" s="3">
         <v>60</v>
       </c>
       <c r="F19" s="3">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>33</v>
@@ -2047,25 +1720,25 @@
         <v>204</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="E20" s="3">
         <v>60</v>
       </c>
       <c r="F20" s="3">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>33</v>
@@ -2077,25 +1750,25 @@
         <v>205</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="E21" s="3">
         <v>60</v>
       </c>
       <c r="F21" s="3">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>33</v>
@@ -2107,25 +1780,25 @@
         <v>206</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="E22" s="3">
         <v>60</v>
       </c>
       <c r="F22" s="3">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>33</v>
@@ -2137,25 +1810,25 @@
         <v>207</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="E23" s="3">
         <v>60</v>
       </c>
       <c r="F23" s="3">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>33</v>
@@ -2167,25 +1840,25 @@
         <v>208</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="E24" s="3">
         <v>60</v>
       </c>
       <c r="F24" s="3">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>33</v>
@@ -2197,25 +1870,25 @@
         <v>209</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="E25" s="3">
         <v>60</v>
       </c>
       <c r="F25" s="3">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>33</v>
@@ -2227,25 +1900,25 @@
         <v>210</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="E26" s="3">
         <v>60</v>
       </c>
       <c r="F26" s="3">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>33</v>
@@ -2257,25 +1930,25 @@
         <v>211</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="E27" s="3">
         <v>60</v>
       </c>
       <c r="F27" s="3">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>101</v>
+        <v>32</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>33</v>
@@ -2287,25 +1960,25 @@
         <v>212</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>102</v>
+        <v>28</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="E28" s="3">
         <v>60</v>
       </c>
       <c r="F28" s="3">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>33</v>
@@ -2317,25 +1990,25 @@
         <v>213</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="E29" s="3">
         <v>60</v>
       </c>
       <c r="F29" s="3">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>33</v>
@@ -2347,25 +2020,25 @@
         <v>214</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="E30" s="3">
         <v>60</v>
       </c>
       <c r="F30" s="3">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>33</v>
@@ -2377,25 +2050,25 @@
         <v>215</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="E31" s="3">
         <v>60</v>
       </c>
       <c r="F31" s="3">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>112</v>
+        <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>113</v>
+        <v>32</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>33</v>
@@ -2407,25 +2080,25 @@
         <v>216</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="E32" s="3">
         <v>60</v>
       </c>
       <c r="F32" s="3">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>115</v>
+        <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>116</v>
+        <v>32</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>33</v>
@@ -2437,25 +2110,25 @@
         <v>217</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>117</v>
+        <v>28</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="E33" s="3">
         <v>60</v>
       </c>
       <c r="F33" s="3">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>118</v>
+        <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>33</v>
@@ -2467,25 +2140,25 @@
         <v>218</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="E34" s="3">
         <v>60</v>
       </c>
       <c r="F34" s="3">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>33</v>
@@ -2497,25 +2170,25 @@
         <v>301</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="E35" s="3">
         <v>120</v>
       </c>
       <c r="F35" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>126</v>
+        <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>33</v>
@@ -2527,25 +2200,25 @@
         <v>302</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="E36" s="3">
         <v>120</v>
       </c>
       <c r="F36" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>129</v>
+        <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="J36" s="3" t="s">
         <v>33</v>
@@ -2557,25 +2230,25 @@
         <v>303</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="E37" s="3">
         <v>120</v>
       </c>
       <c r="F37" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>133</v>
+        <v>32</v>
       </c>
       <c r="J37" s="3" t="s">
         <v>33</v>
@@ -2587,25 +2260,25 @@
         <v>304</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>134</v>
+        <v>28</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="E38" s="3">
         <v>120</v>
       </c>
       <c r="F38" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>136</v>
+        <v>32</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>33</v>
@@ -2617,25 +2290,25 @@
         <v>305</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>137</v>
+        <v>28</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="E39" s="3">
         <v>120</v>
       </c>
       <c r="F39" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>138</v>
+        <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>139</v>
+        <v>32</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>33</v>
@@ -2647,25 +2320,25 @@
         <v>306</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="E40" s="3">
         <v>120</v>
       </c>
       <c r="F40" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>141</v>
+        <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>142</v>
+        <v>32</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>33</v>
@@ -2677,25 +2350,25 @@
         <v>401</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>144</v>
+        <v>39</v>
       </c>
       <c r="E41" s="3">
         <v>60</v>
       </c>
       <c r="F41" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>145</v>
+        <v>40</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>146</v>
+        <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>147</v>
+        <v>32</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>33</v>
@@ -2707,25 +2380,25 @@
         <v>402</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>148</v>
+        <v>41</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>144</v>
+        <v>39</v>
       </c>
       <c r="E42" s="3">
         <v>120</v>
       </c>
       <c r="F42" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>149</v>
+        <v>42</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>33</v>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -55,9 +55,6 @@
     <t>PrefabResourcePath</t>
   </si>
   <si>
-    <t>TestPrefabResourcePath</t>
-  </si>
-  <si>
     <t>Comment</t>
   </si>
   <si>
@@ -109,9 +106,6 @@
     <t>预制体资源路径</t>
   </si>
   <si>
-    <t>测试预制体资源路径</t>
-  </si>
-  <si>
     <t>备注</t>
   </si>
   <si>
@@ -124,10 +118,7 @@
     <t>Meat:1|Bullet:0|Coin:0|Energy:1</t>
   </si>
   <si>
-    <t>Arts/Animals/Prefabs/Animal_Forest_Small_Rabbit</t>
-  </si>
-  <si>
-    <t>Arts/Animals/Prefabs/Animal_Forest_Small_Rabbit_Test</t>
+    <t>Arts/Animals/Prefabs/pf_animal_forest_small_rabbit</t>
   </si>
   <si>
     <t>/</t>
@@ -139,10 +130,16 @@
     <t>Meat:5|Bullet:0|Coin:0|Energy:2</t>
   </si>
   <si>
+    <t>Arts/Animals/Prefabs/pf_animal_forest_medium_deer</t>
+  </si>
+  <si>
     <t>Large</t>
   </si>
   <si>
     <t>Meat:10|Bullet:0|Coin:0|Energy:5</t>
+  </si>
+  <si>
+    <t>Arts/Animals/Prefabs/pf_animal_forest_large_yak</t>
   </si>
   <si>
     <t>弹药怪</t>
@@ -1127,16 +1124,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="6" width="28.625" customWidth="1"/>
     <col min="7" max="7" width="62.7833333333333" customWidth="1"/>
-    <col min="8" max="9" width="48.625" customWidth="1"/>
-    <col min="10" max="10" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="78.625" customWidth="1"/>
+    <col min="9" max="9" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:10">
+    <row r="1" ht="28" customHeight="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1164,116 +1161,104 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:9">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" ht="28" customHeight="1" spans="1:10">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:9">
+      <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:10">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:9">
+      <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:10">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:10">
+    </row>
+    <row r="5" ht="28" customHeight="1" spans="1:9">
       <c r="A5" s="3"/>
       <c r="B5" s="3">
         <v>101</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E5" s="3">
         <v>30</v>
@@ -1282,28 +1267,25 @@
         <v>2</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:9">
       <c r="A6" s="3"/>
       <c r="B6" s="3">
         <v>102</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3">
         <v>30</v>
@@ -1312,28 +1294,25 @@
         <v>2</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:9">
       <c r="A7" s="3"/>
       <c r="B7" s="3">
         <v>103</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E7" s="3">
         <v>30</v>
@@ -1342,28 +1321,25 @@
         <v>2</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1" spans="1:9">
       <c r="A8" s="3"/>
       <c r="B8" s="3">
         <v>104</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E8" s="3">
         <v>30</v>
@@ -1372,28 +1348,25 @@
         <v>2</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1" spans="1:9">
       <c r="A9" s="3"/>
       <c r="B9" s="3">
         <v>105</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E9" s="3">
         <v>30</v>
@@ -1402,28 +1375,25 @@
         <v>2</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:9">
       <c r="A10" s="3"/>
       <c r="B10" s="3">
         <v>106</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E10" s="3">
         <v>30</v>
@@ -1432,28 +1402,25 @@
         <v>2</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:9">
       <c r="A11" s="3"/>
       <c r="B11" s="3">
         <v>107</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E11" s="3">
         <v>30</v>
@@ -1462,28 +1429,25 @@
         <v>2</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:9">
       <c r="A12" s="3"/>
       <c r="B12" s="3">
         <v>108</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E12" s="3">
         <v>30</v>
@@ -1492,28 +1456,25 @@
         <v>2</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:9">
       <c r="A13" s="3"/>
       <c r="B13" s="3">
         <v>109</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E13" s="3">
         <v>30</v>
@@ -1522,28 +1483,25 @@
         <v>2</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1" spans="1:9">
       <c r="A14" s="3"/>
       <c r="B14" s="3">
         <v>110</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E14" s="3">
         <v>30</v>
@@ -1552,28 +1510,25 @@
         <v>2</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1" spans="1:9">
       <c r="A15" s="3"/>
       <c r="B15" s="3">
         <v>111</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E15" s="3">
         <v>30</v>
@@ -1582,28 +1537,25 @@
         <v>2</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:9">
       <c r="A16" s="3"/>
       <c r="B16" s="3">
         <v>112</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E16" s="3">
         <v>30</v>
@@ -1612,28 +1564,25 @@
         <v>2</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="1:9">
       <c r="A17" s="3"/>
       <c r="B17" s="3">
         <v>201</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E17" s="3">
         <v>60</v>
@@ -1642,28 +1591,25 @@
         <v>1.5</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1" spans="1:9">
       <c r="A18" s="3"/>
       <c r="B18" s="3">
         <v>202</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E18" s="3">
         <v>60</v>
@@ -1672,28 +1618,25 @@
         <v>1.5</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1" spans="1:9">
       <c r="A19" s="3"/>
       <c r="B19" s="3">
         <v>203</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E19" s="3">
         <v>60</v>
@@ -1702,28 +1645,25 @@
         <v>1.5</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1" spans="1:9">
       <c r="A20" s="3"/>
       <c r="B20" s="3">
         <v>204</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E20" s="3">
         <v>60</v>
@@ -1732,28 +1672,25 @@
         <v>1.5</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1" spans="1:9">
       <c r="A21" s="3"/>
       <c r="B21" s="3">
         <v>205</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E21" s="3">
         <v>60</v>
@@ -1762,28 +1699,25 @@
         <v>1.5</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1" spans="1:9">
       <c r="A22" s="3"/>
       <c r="B22" s="3">
         <v>206</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E22" s="3">
         <v>60</v>
@@ -1792,28 +1726,25 @@
         <v>1.5</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:9">
       <c r="A23" s="3"/>
       <c r="B23" s="3">
         <v>207</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E23" s="3">
         <v>60</v>
@@ -1822,28 +1753,25 @@
         <v>1.5</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1" spans="1:9">
       <c r="A24" s="3"/>
       <c r="B24" s="3">
         <v>208</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E24" s="3">
         <v>60</v>
@@ -1852,28 +1780,25 @@
         <v>1.5</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1" spans="1:9">
       <c r="A25" s="3"/>
       <c r="B25" s="3">
         <v>209</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E25" s="3">
         <v>60</v>
@@ -1882,28 +1807,25 @@
         <v>1.5</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1" spans="1:9">
       <c r="A26" s="3"/>
       <c r="B26" s="3">
         <v>210</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E26" s="3">
         <v>60</v>
@@ -1912,28 +1834,25 @@
         <v>1.5</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1" spans="1:9">
       <c r="A27" s="3"/>
       <c r="B27" s="3">
         <v>211</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E27" s="3">
         <v>60</v>
@@ -1942,28 +1861,25 @@
         <v>1.5</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1" spans="1:9">
       <c r="A28" s="3"/>
       <c r="B28" s="3">
         <v>212</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E28" s="3">
         <v>60</v>
@@ -1972,28 +1888,25 @@
         <v>1.5</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1" spans="1:9">
       <c r="A29" s="3"/>
       <c r="B29" s="3">
         <v>213</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E29" s="3">
         <v>60</v>
@@ -2002,28 +1915,25 @@
         <v>1.5</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1" spans="1:9">
       <c r="A30" s="3"/>
       <c r="B30" s="3">
         <v>214</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E30" s="3">
         <v>60</v>
@@ -2032,28 +1942,25 @@
         <v>1.5</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1" spans="1:9">
       <c r="A31" s="3"/>
       <c r="B31" s="3">
         <v>215</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E31" s="3">
         <v>60</v>
@@ -2062,28 +1969,25 @@
         <v>1.5</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1" spans="1:9">
       <c r="A32" s="3"/>
       <c r="B32" s="3">
         <v>216</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E32" s="3">
         <v>60</v>
@@ -2092,28 +1996,25 @@
         <v>1.5</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1" spans="1:9">
       <c r="A33" s="3"/>
       <c r="B33" s="3">
         <v>217</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E33" s="3">
         <v>60</v>
@@ -2122,28 +2023,25 @@
         <v>1.5</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1" spans="1:9">
       <c r="A34" s="3"/>
       <c r="B34" s="3">
         <v>218</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E34" s="3">
         <v>60</v>
@@ -2152,28 +2050,25 @@
         <v>1.5</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1" spans="1:9">
       <c r="A35" s="3"/>
       <c r="B35" s="3">
         <v>301</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E35" s="3">
         <v>120</v>
@@ -2182,28 +2077,25 @@
         <v>1</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1" spans="1:9">
       <c r="A36" s="3"/>
       <c r="B36" s="3">
         <v>302</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E36" s="3">
         <v>120</v>
@@ -2212,28 +2104,25 @@
         <v>1</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1" spans="1:9">
       <c r="A37" s="3"/>
       <c r="B37" s="3">
         <v>303</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E37" s="3">
         <v>120</v>
@@ -2242,28 +2131,25 @@
         <v>1</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1" spans="1:9">
       <c r="A38" s="3"/>
       <c r="B38" s="3">
         <v>304</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E38" s="3">
         <v>120</v>
@@ -2272,28 +2158,25 @@
         <v>1</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1" spans="1:9">
       <c r="A39" s="3"/>
       <c r="B39" s="3">
         <v>305</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E39" s="3">
         <v>120</v>
@@ -2302,28 +2185,25 @@
         <v>1</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1" spans="1:9">
       <c r="A40" s="3"/>
       <c r="B40" s="3">
         <v>306</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E40" s="3">
         <v>120</v>
@@ -2332,28 +2212,25 @@
         <v>1</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1" spans="1:9">
       <c r="A41" s="3"/>
       <c r="B41" s="3">
         <v>401</v>
       </c>
       <c r="C41" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>39</v>
       </c>
       <c r="E41" s="3">
         <v>60</v>
@@ -2362,28 +2239,25 @@
         <v>1</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1" spans="1:10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1" spans="1:9">
       <c r="A42" s="3"/>
       <c r="B42" s="3">
         <v>402</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E42" s="3">
         <v>120</v>
@@ -2392,16 +2266,13 @@
         <v>1</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -155,6 +155,18 @@
   </si>
   <si>
     <t>Meat:10|Bullet:0|Coin:10|Energy:5</t>
+  </si>
+  <si>
+    <t>超级大兔子</t>
+  </si>
+  <si>
+    <t>Boss</t>
+  </si>
+  <si>
+    <t>Meat:200|Bullet:0|Coin:20|Energy:0</t>
+  </si>
+  <si>
+    <t>Arts/Animals/Prefabs/pf_animal_snow_boss_rabbit_test</t>
   </si>
 </sst>
 </file>
@@ -1124,7 +1136,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="6" width="28.625" customWidth="1"/>
@@ -2274,6 +2286,42 @@
       <c r="I42" s="3" t="s">
         <v>30</v>
       </c>
+    </row>
+    <row r="43" ht="17.25" spans="2:9">
+      <c r="B43" s="3">
+        <v>501</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F43" s="3">
+        <v>6</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" ht="17.25" spans="2:9">
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -166,7 +166,7 @@
     <t>Meat:200|Bullet:0|Coin:20|Energy:0</t>
   </si>
   <si>
-    <t>Arts/Animals/Prefabs/pf_animal_snow_boss_rabbit_test</t>
+    <t>Arts/Animals/Prefabs/pf_animal_snow_boss_rabbit</t>
   </si>
 </sst>
 </file>
@@ -1273,7 +1273,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="3">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F5" s="3">
         <v>2</v>
@@ -1300,7 +1300,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="3">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F6" s="3">
         <v>2</v>
@@ -1327,7 +1327,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="3">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F7" s="3">
         <v>2</v>
@@ -1354,7 +1354,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="3">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F8" s="3">
         <v>2</v>
@@ -1381,7 +1381,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="3">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F9" s="3">
         <v>2</v>
@@ -1408,7 +1408,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="3">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F10" s="3">
         <v>2</v>
@@ -1435,7 +1435,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="3">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F11" s="3">
         <v>2</v>
@@ -1462,7 +1462,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="3">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F12" s="3">
         <v>2</v>
@@ -1489,7 +1489,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="3">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F13" s="3">
         <v>2</v>
@@ -1516,7 +1516,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="3">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F14" s="3">
         <v>2</v>
@@ -1543,7 +1543,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="3">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
         <v>2</v>
@@ -1570,7 +1570,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="3">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F16" s="3">
         <v>2</v>
@@ -1597,7 +1597,7 @@
         <v>31</v>
       </c>
       <c r="E17" s="3">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F17" s="3">
         <v>1.5</v>
@@ -1624,7 +1624,7 @@
         <v>31</v>
       </c>
       <c r="E18" s="3">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F18" s="3">
         <v>1.5</v>
@@ -1651,7 +1651,7 @@
         <v>31</v>
       </c>
       <c r="E19" s="3">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F19" s="3">
         <v>1.5</v>
@@ -1678,7 +1678,7 @@
         <v>31</v>
       </c>
       <c r="E20" s="3">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F20" s="3">
         <v>1.5</v>
@@ -1705,7 +1705,7 @@
         <v>31</v>
       </c>
       <c r="E21" s="3">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F21" s="3">
         <v>1.5</v>
@@ -1732,7 +1732,7 @@
         <v>31</v>
       </c>
       <c r="E22" s="3">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F22" s="3">
         <v>1.5</v>
@@ -1759,7 +1759,7 @@
         <v>31</v>
       </c>
       <c r="E23" s="3">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F23" s="3">
         <v>1.5</v>
@@ -1786,7 +1786,7 @@
         <v>31</v>
       </c>
       <c r="E24" s="3">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F24" s="3">
         <v>1.5</v>
@@ -1813,7 +1813,7 @@
         <v>31</v>
       </c>
       <c r="E25" s="3">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F25" s="3">
         <v>1.5</v>
@@ -1840,7 +1840,7 @@
         <v>31</v>
       </c>
       <c r="E26" s="3">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F26" s="3">
         <v>1.5</v>
@@ -1867,7 +1867,7 @@
         <v>31</v>
       </c>
       <c r="E27" s="3">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F27" s="3">
         <v>1.5</v>
@@ -1894,7 +1894,7 @@
         <v>31</v>
       </c>
       <c r="E28" s="3">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F28" s="3">
         <v>1.5</v>
@@ -1921,7 +1921,7 @@
         <v>31</v>
       </c>
       <c r="E29" s="3">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F29" s="3">
         <v>1.5</v>
@@ -1948,7 +1948,7 @@
         <v>31</v>
       </c>
       <c r="E30" s="3">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F30" s="3">
         <v>1.5</v>
@@ -1975,7 +1975,7 @@
         <v>31</v>
       </c>
       <c r="E31" s="3">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F31" s="3">
         <v>1.5</v>
@@ -2002,7 +2002,7 @@
         <v>31</v>
       </c>
       <c r="E32" s="3">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F32" s="3">
         <v>1.5</v>
@@ -2029,7 +2029,7 @@
         <v>31</v>
       </c>
       <c r="E33" s="3">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F33" s="3">
         <v>1.5</v>
@@ -2056,7 +2056,7 @@
         <v>31</v>
       </c>
       <c r="E34" s="3">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F34" s="3">
         <v>1.5</v>
@@ -2083,7 +2083,7 @@
         <v>34</v>
       </c>
       <c r="E35" s="3">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="F35" s="3">
         <v>1</v>
@@ -2110,7 +2110,7 @@
         <v>34</v>
       </c>
       <c r="E36" s="3">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="F36" s="3">
         <v>1</v>
@@ -2137,7 +2137,7 @@
         <v>34</v>
       </c>
       <c r="E37" s="3">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="F37" s="3">
         <v>1</v>
@@ -2164,7 +2164,7 @@
         <v>34</v>
       </c>
       <c r="E38" s="3">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="F38" s="3">
         <v>1</v>
@@ -2191,7 +2191,7 @@
         <v>34</v>
       </c>
       <c r="E39" s="3">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="F39" s="3">
         <v>1</v>
@@ -2218,7 +2218,7 @@
         <v>34</v>
       </c>
       <c r="E40" s="3">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="F40" s="3">
         <v>1</v>
@@ -2245,7 +2245,7 @@
         <v>38</v>
       </c>
       <c r="E41" s="3">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="F41" s="3">
         <v>1</v>
@@ -2272,7 +2272,7 @@
         <v>38</v>
       </c>
       <c r="E42" s="3">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="F42" s="3">
         <v>1</v>
@@ -2287,7 +2287,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" ht="17.25" spans="2:9">
+    <row r="43" ht="17.25" spans="1:9">
       <c r="B43" s="3">
         <v>501</v>
       </c>
@@ -2313,7 +2313,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" ht="17.25" spans="2:9">
+    <row r="44" ht="17.25" spans="1:9">
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="52">
   <si>
     <t>##var</t>
   </si>
@@ -55,6 +55,9 @@
     <t>PrefabResourcePath</t>
   </si>
   <si>
+    <t>EffectPrefabPath</t>
+  </si>
+  <si>
     <t>Comment</t>
   </si>
   <si>
@@ -106,6 +109,9 @@
     <t>预制体资源路径</t>
   </si>
   <si>
+    <t>特效预制体路径</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -121,6 +127,9 @@
     <t>Arts/Animals/Prefabs/pf_animal_forest_small_rabbit</t>
   </si>
   <si>
+    <t>Arts/Effects/Prefabs/FX_JXTX001_01</t>
+  </si>
+  <si>
     <t>/</t>
   </si>
   <si>
@@ -151,12 +160,18 @@
     <t>Meat:5|Bullet:1|Coin:0|Energy:5</t>
   </si>
   <si>
+    <t>Arts/Effects/Prefabs/FX_IPJSTX001</t>
+  </si>
+  <si>
     <t>金币怪</t>
   </si>
   <si>
     <t>Meat:10|Bullet:0|Coin:10|Energy:5</t>
   </si>
   <si>
+    <t>Arts/Effects/Prefabs/FX_IPJSTX002_1</t>
+  </si>
+  <si>
     <t>超级大兔子</t>
   </si>
   <si>
@@ -167,6 +182,9 @@
   </si>
   <si>
     <t>Arts/Animals/Prefabs/pf_animal_snow_boss_rabbit</t>
+  </si>
+  <si>
+    <t>Arts/Effects/Prefabs/FX_JXTX001_03</t>
   </si>
 </sst>
 </file>
@@ -1136,16 +1154,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="6" width="28.625" customWidth="1"/>
     <col min="7" max="7" width="62.7833333333333" customWidth="1"/>
     <col min="8" max="8" width="78.625" customWidth="1"/>
-    <col min="9" max="9" width="28.625" customWidth="1"/>
+    <col min="9" max="9" width="48.625" customWidth="1"/>
+    <col min="10" max="10" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:9">
+    <row r="1" ht="28" customHeight="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1173,104 +1192,116 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" ht="28" customHeight="1" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:9">
+        <v>12</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:9">
+        <v>17</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:9">
+        <v>26</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1" spans="1:10">
       <c r="A5" s="3"/>
       <c r="B5" s="3">
         <v>101</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E5" s="3">
         <v>100</v>
@@ -1279,25 +1310,28 @@
         <v>2</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:10">
       <c r="A6" s="3"/>
       <c r="B6" s="3">
         <v>102</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E6" s="3">
         <v>100</v>
@@ -1306,25 +1340,28 @@
         <v>2</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:10">
       <c r="A7" s="3"/>
       <c r="B7" s="3">
         <v>103</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E7" s="3">
         <v>100</v>
@@ -1333,25 +1370,28 @@
         <v>2</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1" spans="1:10">
       <c r="A8" s="3"/>
       <c r="B8" s="3">
         <v>104</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
@@ -1360,25 +1400,28 @@
         <v>2</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1" spans="1:10">
       <c r="A9" s="3"/>
       <c r="B9" s="3">
         <v>105</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E9" s="3">
         <v>100</v>
@@ -1387,25 +1430,28 @@
         <v>2</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:10">
       <c r="A10" s="3"/>
       <c r="B10" s="3">
         <v>106</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E10" s="3">
         <v>100</v>
@@ -1414,25 +1460,28 @@
         <v>2</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:10">
       <c r="A11" s="3"/>
       <c r="B11" s="3">
         <v>107</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E11" s="3">
         <v>100</v>
@@ -1441,25 +1490,28 @@
         <v>2</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:10">
       <c r="A12" s="3"/>
       <c r="B12" s="3">
         <v>108</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E12" s="3">
         <v>100</v>
@@ -1468,25 +1520,28 @@
         <v>2</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:10">
       <c r="A13" s="3"/>
       <c r="B13" s="3">
         <v>109</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E13" s="3">
         <v>100</v>
@@ -1495,25 +1550,28 @@
         <v>2</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1" spans="1:10">
       <c r="A14" s="3"/>
       <c r="B14" s="3">
         <v>110</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E14" s="3">
         <v>100</v>
@@ -1522,25 +1580,28 @@
         <v>2</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1" spans="1:10">
       <c r="A15" s="3"/>
       <c r="B15" s="3">
         <v>111</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E15" s="3">
         <v>100</v>
@@ -1549,25 +1610,28 @@
         <v>2</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:10">
       <c r="A16" s="3"/>
       <c r="B16" s="3">
         <v>112</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E16" s="3">
         <v>100</v>
@@ -1576,25 +1640,28 @@
         <v>2</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="1:10">
       <c r="A17" s="3"/>
       <c r="B17" s="3">
         <v>201</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E17" s="3">
         <v>200</v>
@@ -1603,25 +1670,28 @@
         <v>1.5</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1" spans="1:10">
       <c r="A18" s="3"/>
       <c r="B18" s="3">
         <v>202</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E18" s="3">
         <v>200</v>
@@ -1630,25 +1700,28 @@
         <v>1.5</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1" spans="1:10">
       <c r="A19" s="3"/>
       <c r="B19" s="3">
         <v>203</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E19" s="3">
         <v>200</v>
@@ -1657,25 +1730,28 @@
         <v>1.5</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1" spans="1:10">
       <c r="A20" s="3"/>
       <c r="B20" s="3">
         <v>204</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E20" s="3">
         <v>200</v>
@@ -1684,25 +1760,28 @@
         <v>1.5</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1" spans="1:10">
       <c r="A21" s="3"/>
       <c r="B21" s="3">
         <v>205</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E21" s="3">
         <v>200</v>
@@ -1711,25 +1790,28 @@
         <v>1.5</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1" spans="1:10">
       <c r="A22" s="3"/>
       <c r="B22" s="3">
         <v>206</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E22" s="3">
         <v>200</v>
@@ -1738,25 +1820,28 @@
         <v>1.5</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:10">
       <c r="A23" s="3"/>
       <c r="B23" s="3">
         <v>207</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E23" s="3">
         <v>200</v>
@@ -1765,25 +1850,28 @@
         <v>1.5</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1" spans="1:10">
       <c r="A24" s="3"/>
       <c r="B24" s="3">
         <v>208</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E24" s="3">
         <v>200</v>
@@ -1792,25 +1880,28 @@
         <v>1.5</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1" spans="1:10">
       <c r="A25" s="3"/>
       <c r="B25" s="3">
         <v>209</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E25" s="3">
         <v>200</v>
@@ -1819,25 +1910,28 @@
         <v>1.5</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1" spans="1:10">
       <c r="A26" s="3"/>
       <c r="B26" s="3">
         <v>210</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E26" s="3">
         <v>200</v>
@@ -1846,25 +1940,28 @@
         <v>1.5</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1" spans="1:10">
       <c r="A27" s="3"/>
       <c r="B27" s="3">
         <v>211</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E27" s="3">
         <v>200</v>
@@ -1873,25 +1970,28 @@
         <v>1.5</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1" spans="1:10">
       <c r="A28" s="3"/>
       <c r="B28" s="3">
         <v>212</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E28" s="3">
         <v>200</v>
@@ -1900,25 +2000,28 @@
         <v>1.5</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1" spans="1:10">
       <c r="A29" s="3"/>
       <c r="B29" s="3">
         <v>213</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E29" s="3">
         <v>200</v>
@@ -1927,25 +2030,28 @@
         <v>1.5</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1" spans="1:10">
       <c r="A30" s="3"/>
       <c r="B30" s="3">
         <v>214</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E30" s="3">
         <v>200</v>
@@ -1954,25 +2060,28 @@
         <v>1.5</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1" spans="1:10">
       <c r="A31" s="3"/>
       <c r="B31" s="3">
         <v>215</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E31" s="3">
         <v>200</v>
@@ -1981,25 +2090,28 @@
         <v>1.5</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1" spans="1:10">
       <c r="A32" s="3"/>
       <c r="B32" s="3">
         <v>216</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E32" s="3">
         <v>200</v>
@@ -2008,25 +2120,28 @@
         <v>1.5</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1" spans="1:10">
       <c r="A33" s="3"/>
       <c r="B33" s="3">
         <v>217</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E33" s="3">
         <v>200</v>
@@ -2035,25 +2150,28 @@
         <v>1.5</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1" spans="1:10">
       <c r="A34" s="3"/>
       <c r="B34" s="3">
         <v>218</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E34" s="3">
         <v>200</v>
@@ -2062,25 +2180,28 @@
         <v>1.5</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1" spans="1:10">
       <c r="A35" s="3"/>
       <c r="B35" s="3">
         <v>301</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E35" s="3">
         <v>300</v>
@@ -2089,25 +2210,28 @@
         <v>1</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1" spans="1:10">
       <c r="A36" s="3"/>
       <c r="B36" s="3">
         <v>302</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E36" s="3">
         <v>300</v>
@@ -2116,25 +2240,28 @@
         <v>1</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1" spans="1:10">
       <c r="A37" s="3"/>
       <c r="B37" s="3">
         <v>303</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E37" s="3">
         <v>300</v>
@@ -2143,25 +2270,28 @@
         <v>1</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1" spans="1:10">
       <c r="A38" s="3"/>
       <c r="B38" s="3">
         <v>304</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E38" s="3">
         <v>300</v>
@@ -2170,25 +2300,28 @@
         <v>1</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1" spans="1:10">
       <c r="A39" s="3"/>
       <c r="B39" s="3">
         <v>305</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E39" s="3">
         <v>300</v>
@@ -2197,25 +2330,28 @@
         <v>1</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1" spans="1:10">
       <c r="A40" s="3"/>
       <c r="B40" s="3">
         <v>306</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E40" s="3">
         <v>300</v>
@@ -2224,25 +2360,28 @@
         <v>1</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1" spans="1:9">
+        <v>32</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1" spans="1:10">
       <c r="A41" s="3"/>
       <c r="B41" s="3">
         <v>401</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E41" s="3">
         <v>300</v>
@@ -2251,25 +2390,28 @@
         <v>1</v>
       </c>
       <c r="G41" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="I41" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1" spans="1:9">
+        <v>43</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1" spans="1:10">
       <c r="A42" s="3"/>
       <c r="B42" s="3">
         <v>402</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E42" s="3">
         <v>300</v>
@@ -2278,24 +2420,27 @@
         <v>1</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="43" ht="17.25" spans="1:9">
+        <v>46</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" ht="17.25" spans="2:10">
       <c r="B43" s="3">
         <v>501</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E43" s="3">
         <v>1000</v>
@@ -2304,16 +2449,19 @@
         <v>6</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="44" ht="17.25" spans="1:9">
+        <v>51</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" ht="17.25" spans="2:10">
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
@@ -2322,6 +2470,7 @@
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="53">
   <si>
     <t>##var</t>
   </si>
@@ -124,7 +124,7 @@
     <t>Meat:1|Bullet:0|Coin:0|Energy:1</t>
   </si>
   <si>
-    <t>Arts/Animals/Prefabs/pf_animal_forest_small_rabbit</t>
+    <t>Arts/Animals/Prefabs/pf_animal_forest_small_coin</t>
   </si>
   <si>
     <t>Arts/Effects/Prefabs/FX_JXTX001_01</t>
@@ -139,7 +139,7 @@
     <t>Meat:5|Bullet:0|Coin:0|Energy:2</t>
   </si>
   <si>
-    <t>Arts/Animals/Prefabs/pf_animal_forest_medium_deer</t>
+    <t>Arts/Animals/Prefabs/pf_animal_forest_medium_coin</t>
   </si>
   <si>
     <t>Large</t>
@@ -148,7 +148,7 @@
     <t>Meat:10|Bullet:0|Coin:0|Energy:5</t>
   </si>
   <si>
-    <t>Arts/Animals/Prefabs/pf_animal_forest_large_yak</t>
+    <t>Arts/Animals/Prefabs/pf_animal_forest_large_coin</t>
   </si>
   <si>
     <t>弹药怪</t>
@@ -160,6 +160,9 @@
     <t>Meat:5|Bullet:1|Coin:0|Energy:5</t>
   </si>
   <si>
+    <t>Arts/Animals/Prefabs/pf_animal_forest_special_bulletcoin</t>
+  </si>
+  <si>
     <t>Arts/Effects/Prefabs/FX_IPJSTX001</t>
   </si>
   <si>
@@ -169,6 +172,9 @@
     <t>Meat:10|Bullet:0|Coin:10|Energy:5</t>
   </si>
   <si>
+    <t>Arts/Animals/Prefabs/pf_animal_forest_special_threekpcoin</t>
+  </si>
+  <si>
     <t>Arts/Effects/Prefabs/FX_IPJSTX002_1</t>
   </si>
   <si>
@@ -179,9 +185,6 @@
   </si>
   <si>
     <t>Meat:200|Bullet:0|Coin:20|Energy:0</t>
-  </si>
-  <si>
-    <t>Arts/Animals/Prefabs/pf_animal_snow_boss_rabbit</t>
   </si>
   <si>
     <t>Arts/Effects/Prefabs/FX_JXTX001_03</t>
@@ -2393,10 +2396,10 @@
         <v>42</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>33</v>
@@ -2408,7 +2411,7 @@
         <v>402</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>41</v>
@@ -2420,27 +2423,27 @@
         <v>1</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="43" ht="17.25" spans="2:10">
+    <row r="43" ht="17.25" spans="1:10">
       <c r="B43" s="3">
         <v>501</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E43" s="3">
         <v>1000</v>
@@ -2449,19 +2452,19 @@
         <v>6</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="44" ht="17.25" spans="2:10">
+    <row r="44" ht="17.25" spans="1:10">
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -121,7 +121,7 @@
     <t>Small</t>
   </si>
   <si>
-    <t>Meat:1|Bullet:0|Coin:0|Energy:1</t>
+    <t>Meat:3|Bullet:0|Coin:0|Energy:2</t>
   </si>
   <si>
     <t>Arts/Animals/Prefabs/pf_animal_forest_small_coin</t>
@@ -136,7 +136,7 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>Meat:5|Bullet:0|Coin:0|Energy:2</t>
+    <t>Meat:6|Bullet:0|Coin:0|Energy:4</t>
   </si>
   <si>
     <t>Arts/Animals/Prefabs/pf_animal_forest_medium_coin</t>
@@ -145,7 +145,7 @@
     <t>Large</t>
   </si>
   <si>
-    <t>Meat:10|Bullet:0|Coin:0|Energy:5</t>
+    <t>Meat:20|Bullet:0|Coin:0|Energy:10</t>
   </si>
   <si>
     <t>Arts/Animals/Prefabs/pf_animal_forest_large_coin</t>
@@ -157,7 +157,7 @@
     <t>Special</t>
   </si>
   <si>
-    <t>Meat:5|Bullet:1|Coin:0|Energy:5</t>
+    <t>Meat:20|Bullet:1|Coin:0|Energy:10</t>
   </si>
   <si>
     <t>Arts/Animals/Prefabs/pf_animal_forest_special_bulletcoin</t>
@@ -169,9 +169,6 @@
     <t>金币怪</t>
   </si>
   <si>
-    <t>Meat:10|Bullet:0|Coin:10|Energy:5</t>
-  </si>
-  <si>
     <t>Arts/Animals/Prefabs/pf_animal_forest_special_threekpcoin</t>
   </si>
   <si>
@@ -182,9 +179,6 @@
   </si>
   <si>
     <t>Boss</t>
-  </si>
-  <si>
-    <t>Meat:200|Bullet:0|Coin:20|Energy:0</t>
   </si>
   <si>
     <t>Arts/Effects/Prefabs/FX_JXTX001_03</t>
@@ -2423,13 +2417,13 @@
         <v>1</v>
       </c>
       <c r="G42" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H42" s="3" t="s">
+      <c r="I42" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>33</v>
@@ -2440,10 +2434,10 @@
         <v>501</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="E43" s="3">
         <v>1000</v>
@@ -2452,13 +2446,13 @@
         <v>6</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>39</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>33</v>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="59">
   <si>
     <t>##var</t>
   </si>
@@ -40,7 +40,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>VolumeType</t>
+    <t>SpecieType</t>
   </si>
   <si>
     <t>HP</t>
@@ -49,6 +49,9 @@
     <t>MoveSpeed</t>
   </si>
   <si>
+    <t>StayTime</t>
+  </si>
+  <si>
     <t>DropRewards</t>
   </si>
   <si>
@@ -70,7 +73,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>HuntingConfig.Enum.EVolumeType</t>
+    <t>HuntingConfig.Enum.ESpecieType</t>
   </si>
   <si>
     <t>float</t>
@@ -94,7 +97,7 @@
     <t>物种名称</t>
   </si>
   <si>
-    <t>体型</t>
+    <t>物种类型</t>
   </si>
   <si>
     <t>血量</t>
@@ -103,6 +106,9 @@
     <t>移动速度</t>
   </si>
   <si>
+    <t>驻场时间</t>
+  </si>
+  <si>
     <t>掉落奖励</t>
   </si>
   <si>
@@ -115,13 +121,13 @@
     <t>备注</t>
   </si>
   <si>
-    <t>兔子</t>
+    <t>小兔子</t>
   </si>
   <si>
     <t>Small</t>
   </si>
   <si>
-    <t>Meat:3|Bullet:0|Coin:0|Energy:2</t>
+    <t>Meat:3|Bullet:0|ThreeKPCoin:0|Energy:2</t>
   </si>
   <si>
     <t>Arts/Animals/Prefabs/pf_animal_forest_small_coin</t>
@@ -133,31 +139,37 @@
     <t>/</t>
   </si>
   <si>
+    <t>中兔子</t>
+  </si>
+  <si>
     <t>Medium</t>
   </si>
   <si>
-    <t>Meat:6|Bullet:0|Coin:0|Energy:4</t>
+    <t>Meat:6|Bullet:0|ThreeKPCoin:0|Energy:4</t>
   </si>
   <si>
     <t>Arts/Animals/Prefabs/pf_animal_forest_medium_coin</t>
   </si>
   <si>
+    <t>大兔子</t>
+  </si>
+  <si>
     <t>Large</t>
   </si>
   <si>
-    <t>Meat:20|Bullet:0|Coin:0|Energy:10</t>
+    <t>Meat:20|Bullet:0|ThreeKPCoin:0|Energy:10</t>
   </si>
   <si>
     <t>Arts/Animals/Prefabs/pf_animal_forest_large_coin</t>
   </si>
   <si>
-    <t>弹药怪</t>
-  </si>
-  <si>
-    <t>Special</t>
-  </si>
-  <si>
-    <t>Meat:20|Bullet:1|Coin:0|Energy:10</t>
+    <t>弹药兔子</t>
+  </si>
+  <si>
+    <t>Bullet</t>
+  </si>
+  <si>
+    <t>Meat:20|Bullet:1|ThreeKPCoin:0|Energy:10</t>
   </si>
   <si>
     <t>Arts/Animals/Prefabs/pf_animal_forest_special_bulletcoin</t>
@@ -166,7 +178,13 @@
     <t>Arts/Effects/Prefabs/FX_IPJSTX001</t>
   </si>
   <si>
-    <t>金币怪</t>
+    <t>金币兔子</t>
+  </si>
+  <si>
+    <t>ThreeKPCoin</t>
+  </si>
+  <si>
+    <t>Meat:0|Bullet:0|ThreeKPCoin:10|Energy:10</t>
   </si>
   <si>
     <t>Arts/Animals/Prefabs/pf_animal_forest_special_threekpcoin</t>
@@ -179,6 +197,12 @@
   </si>
   <si>
     <t>Boss</t>
+  </si>
+  <si>
+    <t>Meat:2000|Bullet:0|ThreeKPCoin:0|Energy:10</t>
+  </si>
+  <si>
+    <t>Arts/Animals/Prefabs/pf_animal_snow_boss_coin</t>
   </si>
   <si>
     <t>Arts/Effects/Prefabs/FX_JXTX001_03</t>
@@ -1151,17 +1175,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="6" width="28.625" customWidth="1"/>
-    <col min="7" max="7" width="62.7833333333333" customWidth="1"/>
-    <col min="8" max="8" width="78.625" customWidth="1"/>
-    <col min="9" max="9" width="48.625" customWidth="1"/>
-    <col min="10" max="10" width="28.625" customWidth="1"/>
+    <col min="1" max="3" width="28.625" customWidth="1"/>
+    <col min="4" max="4" width="48.625" customWidth="1"/>
+    <col min="5" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="62.7833333333333" customWidth="1"/>
+    <col min="9" max="9" width="78.625" customWidth="1"/>
+    <col min="10" max="10" width="48.625" customWidth="1"/>
+    <col min="11" max="11" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:10">
+    <row r="1" ht="28" customHeight="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1192,113 +1218,125 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" ht="28" customHeight="1" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>12</v>
+      <c r="H2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:10">
+        <v>13</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:10">
+        <v>18</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="I4" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="J4" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:10">
+        <v>28</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1" spans="1:11">
       <c r="A5" s="3"/>
       <c r="B5" s="3">
         <v>101</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5" s="3">
         <v>100</v>
@@ -1306,29 +1344,32 @@
       <c r="F5" s="3">
         <v>2</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>30</v>
+      <c r="G5" s="3">
+        <v>10</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:11">
       <c r="A6" s="3"/>
       <c r="B6" s="3">
         <v>102</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E6" s="3">
         <v>100</v>
@@ -1336,29 +1377,32 @@
       <c r="F6" s="3">
         <v>2</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>30</v>
+      <c r="G6" s="3">
+        <v>10</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:11">
       <c r="A7" s="3"/>
       <c r="B7" s="3">
         <v>103</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E7" s="3">
         <v>100</v>
@@ -1366,29 +1410,32 @@
       <c r="F7" s="3">
         <v>2</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>30</v>
+      <c r="G7" s="3">
+        <v>10</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1" spans="1:11">
       <c r="A8" s="3"/>
       <c r="B8" s="3">
         <v>104</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
@@ -1396,29 +1443,32 @@
       <c r="F8" s="3">
         <v>2</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>30</v>
+      <c r="G8" s="3">
+        <v>10</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1" spans="1:11">
       <c r="A9" s="3"/>
       <c r="B9" s="3">
         <v>105</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E9" s="3">
         <v>100</v>
@@ -1426,29 +1476,32 @@
       <c r="F9" s="3">
         <v>2</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>30</v>
+      <c r="G9" s="3">
+        <v>10</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:11">
       <c r="A10" s="3"/>
       <c r="B10" s="3">
         <v>106</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E10" s="3">
         <v>100</v>
@@ -1456,29 +1509,32 @@
       <c r="F10" s="3">
         <v>2</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>30</v>
+      <c r="G10" s="3">
+        <v>10</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:11">
       <c r="A11" s="3"/>
       <c r="B11" s="3">
         <v>107</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E11" s="3">
         <v>100</v>
@@ -1486,29 +1542,32 @@
       <c r="F11" s="3">
         <v>2</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>30</v>
+      <c r="G11" s="3">
+        <v>10</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:11">
       <c r="A12" s="3"/>
       <c r="B12" s="3">
         <v>108</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E12" s="3">
         <v>100</v>
@@ -1516,29 +1575,32 @@
       <c r="F12" s="3">
         <v>2</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>30</v>
+      <c r="G12" s="3">
+        <v>10</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:11">
       <c r="A13" s="3"/>
       <c r="B13" s="3">
         <v>109</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E13" s="3">
         <v>100</v>
@@ -1546,29 +1608,32 @@
       <c r="F13" s="3">
         <v>2</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>30</v>
+      <c r="G13" s="3">
+        <v>10</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1" spans="1:11">
       <c r="A14" s="3"/>
       <c r="B14" s="3">
         <v>110</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E14" s="3">
         <v>100</v>
@@ -1576,89 +1641,98 @@
       <c r="F14" s="3">
         <v>2</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>30</v>
+      <c r="G14" s="3">
+        <v>10</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1" spans="1:11">
       <c r="A15" s="3"/>
       <c r="B15" s="3">
-        <v>111</v>
+        <v>201</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>2</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>30</v>
+        <v>1.5</v>
+      </c>
+      <c r="G15" s="3">
+        <v>16</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:11">
       <c r="A16" s="3"/>
       <c r="B16" s="3">
-        <v>112</v>
+        <v>202</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="E16" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F16" s="3">
-        <v>2</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>30</v>
+        <v>1.5</v>
+      </c>
+      <c r="G16" s="3">
+        <v>16</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="1:11">
       <c r="A17" s="3"/>
       <c r="B17" s="3">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E17" s="3">
         <v>200</v>
@@ -1666,29 +1740,32 @@
       <c r="F17" s="3">
         <v>1.5</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>35</v>
+      <c r="G17" s="3">
+        <v>16</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1" spans="1:11">
       <c r="A18" s="3"/>
       <c r="B18" s="3">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E18" s="3">
         <v>200</v>
@@ -1696,29 +1773,32 @@
       <c r="F18" s="3">
         <v>1.5</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>35</v>
+      <c r="G18" s="3">
+        <v>16</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1" spans="1:11">
       <c r="A19" s="3"/>
       <c r="B19" s="3">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E19" s="3">
         <v>200</v>
@@ -1726,29 +1806,32 @@
       <c r="F19" s="3">
         <v>1.5</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>35</v>
+      <c r="G19" s="3">
+        <v>16</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1" spans="1:11">
       <c r="A20" s="3"/>
       <c r="B20" s="3">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E20" s="3">
         <v>200</v>
@@ -1756,29 +1839,32 @@
       <c r="F20" s="3">
         <v>1.5</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>35</v>
+      <c r="G20" s="3">
+        <v>16</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1" spans="1:11">
       <c r="A21" s="3"/>
       <c r="B21" s="3">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E21" s="3">
         <v>200</v>
@@ -1786,29 +1872,32 @@
       <c r="F21" s="3">
         <v>1.5</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>35</v>
+      <c r="G21" s="3">
+        <v>16</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1" spans="1:11">
       <c r="A22" s="3"/>
       <c r="B22" s="3">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E22" s="3">
         <v>200</v>
@@ -1816,29 +1905,32 @@
       <c r="F22" s="3">
         <v>1.5</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>35</v>
+      <c r="G22" s="3">
+        <v>16</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:11">
       <c r="A23" s="3"/>
       <c r="B23" s="3">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E23" s="3">
         <v>200</v>
@@ -1846,29 +1938,32 @@
       <c r="F23" s="3">
         <v>1.5</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>35</v>
+      <c r="G23" s="3">
+        <v>16</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1" spans="1:11">
       <c r="A24" s="3"/>
       <c r="B24" s="3">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E24" s="3">
         <v>200</v>
@@ -1876,29 +1971,32 @@
       <c r="F24" s="3">
         <v>1.5</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>35</v>
+      <c r="G24" s="3">
+        <v>16</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1" spans="1:11">
       <c r="A25" s="3"/>
       <c r="B25" s="3">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E25" s="3">
         <v>200</v>
@@ -1906,29 +2004,32 @@
       <c r="F25" s="3">
         <v>1.5</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>35</v>
+      <c r="G25" s="3">
+        <v>16</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1" spans="1:11">
       <c r="A26" s="3"/>
       <c r="B26" s="3">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E26" s="3">
         <v>200</v>
@@ -1936,538 +2037,347 @@
       <c r="F26" s="3">
         <v>1.5</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>35</v>
+      <c r="G26" s="3">
+        <v>16</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1" spans="1:11">
       <c r="A27" s="3"/>
       <c r="B27" s="3">
-        <v>211</v>
+        <v>301</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="E27" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F27" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>35</v>
+        <v>1</v>
+      </c>
+      <c r="G27" s="3">
+        <v>30</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1" spans="1:11">
       <c r="A28" s="3"/>
       <c r="B28" s="3">
-        <v>212</v>
+        <v>302</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="E28" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F28" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>35</v>
+        <v>1</v>
+      </c>
+      <c r="G28" s="3">
+        <v>30</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1" spans="1:11">
       <c r="A29" s="3"/>
       <c r="B29" s="3">
-        <v>213</v>
+        <v>303</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="E29" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F29" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>35</v>
+        <v>1</v>
+      </c>
+      <c r="G29" s="3">
+        <v>30</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1" spans="1:11">
       <c r="A30" s="3"/>
       <c r="B30" s="3">
-        <v>214</v>
+        <v>304</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="E30" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F30" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>35</v>
+        <v>1</v>
+      </c>
+      <c r="G30" s="3">
+        <v>30</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1" spans="1:11">
       <c r="A31" s="3"/>
       <c r="B31" s="3">
-        <v>215</v>
+        <v>401</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="E31" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F31" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>35</v>
+        <v>1</v>
+      </c>
+      <c r="G31" s="3">
+        <v>10</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1" spans="1:10">
+        <v>48</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1" spans="1:11">
       <c r="A32" s="3"/>
       <c r="B32" s="3">
-        <v>216</v>
+        <v>402</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E32" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F32" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>35</v>
+        <v>1</v>
+      </c>
+      <c r="G32" s="3">
+        <v>10</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1" spans="1:10">
-      <c r="A33" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1" spans="2:11">
       <c r="B33" s="3">
-        <v>217</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>34</v>
+        <v>501</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="E33" s="3">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="F33" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>35</v>
+        <v>6</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-1</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1" spans="1:10">
-      <c r="A34" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1" spans="2:11">
       <c r="B34" s="3">
-        <v>218</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>34</v>
+        <v>502</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="E34" s="3">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="F34" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>35</v>
+        <v>6</v>
+      </c>
+      <c r="G34" s="3">
+        <v>-1</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1" spans="1:10">
-      <c r="A35" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1" spans="2:11">
       <c r="B35" s="3">
-        <v>301</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>28</v>
+        <v>503</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="E35" s="3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="F35" s="3">
-        <v>1</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>38</v>
+        <v>6</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-1</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1" spans="1:10">
-      <c r="A36" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1" spans="2:11">
       <c r="B36" s="3">
-        <v>302</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>28</v>
+        <v>504</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="E36" s="3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="F36" s="3">
-        <v>1</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>38</v>
+        <v>6</v>
+      </c>
+      <c r="G36" s="3">
+        <v>-1</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1" spans="1:10">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3">
-        <v>303</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E37" s="3">
-        <v>300</v>
-      </c>
-      <c r="F37" s="3">
-        <v>1</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1" spans="1:10">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3">
-        <v>304</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E38" s="3">
-        <v>300</v>
-      </c>
-      <c r="F38" s="3">
-        <v>1</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1" spans="1:10">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3">
-        <v>305</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E39" s="3">
-        <v>300</v>
-      </c>
-      <c r="F39" s="3">
-        <v>1</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1" spans="1:10">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3">
-        <v>306</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E40" s="3">
-        <v>300</v>
-      </c>
-      <c r="F40" s="3">
-        <v>1</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1" spans="1:10">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3">
-        <v>401</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E41" s="3">
-        <v>300</v>
-      </c>
-      <c r="F41" s="3">
-        <v>1</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1" spans="1:10">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3">
-        <v>402</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E42" s="3">
-        <v>300</v>
-      </c>
-      <c r="F42" s="3">
-        <v>1</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="43" ht="17.25" spans="1:10">
-      <c r="B43" s="3">
-        <v>501</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E43" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F43" s="3">
-        <v>6</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="44" ht="17.25" spans="1:10">
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -139,6 +139,12 @@
     <t>/</t>
   </si>
   <si>
+    <t>Arts/Animals/Prefabs/pf_animal_snow_small_coin01</t>
+  </si>
+  <si>
+    <t>Arts/Animals/Prefabs/pf_animal_snow_small_coin02</t>
+  </si>
+  <si>
     <t>中兔子</t>
   </si>
   <si>
@@ -148,7 +154,7 @@
     <t>Meat:6|Bullet:0|ThreeKPCoin:0|Energy:4</t>
   </si>
   <si>
-    <t>Arts/Animals/Prefabs/pf_animal_forest_medium_coin</t>
+    <t>Arts/Animals/Prefabs/pf_animal_forest_medium_pig</t>
   </si>
   <si>
     <t>大兔子</t>
@@ -1615,7 +1621,7 @@
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>34</v>
@@ -1648,7 +1654,7 @@
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>34</v>
@@ -1663,10 +1669,10 @@
         <v>201</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E15" s="3">
         <v>200</v>
@@ -1678,10 +1684,10 @@
         <v>16</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>34</v>
@@ -1696,10 +1702,10 @@
         <v>202</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E16" s="3">
         <v>200</v>
@@ -1711,10 +1717,10 @@
         <v>16</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>34</v>
@@ -1729,10 +1735,10 @@
         <v>203</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E17" s="3">
         <v>200</v>
@@ -1744,10 +1750,10 @@
         <v>16</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>34</v>
@@ -1762,10 +1768,10 @@
         <v>204</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E18" s="3">
         <v>200</v>
@@ -1777,10 +1783,10 @@
         <v>16</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>34</v>
@@ -1795,10 +1801,10 @@
         <v>205</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E19" s="3">
         <v>200</v>
@@ -1810,10 +1816,10 @@
         <v>16</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>34</v>
@@ -1828,10 +1834,10 @@
         <v>206</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E20" s="3">
         <v>200</v>
@@ -1843,10 +1849,10 @@
         <v>16</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>34</v>
@@ -1861,10 +1867,10 @@
         <v>207</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E21" s="3">
         <v>200</v>
@@ -1876,10 +1882,10 @@
         <v>16</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>34</v>
@@ -1894,10 +1900,10 @@
         <v>208</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E22" s="3">
         <v>200</v>
@@ -1909,10 +1915,10 @@
         <v>16</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>34</v>
@@ -1927,10 +1933,10 @@
         <v>209</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E23" s="3">
         <v>200</v>
@@ -1942,10 +1948,10 @@
         <v>16</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>34</v>
@@ -1960,10 +1966,10 @@
         <v>210</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E24" s="3">
         <v>200</v>
@@ -1975,10 +1981,10 @@
         <v>16</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>34</v>
@@ -1993,10 +1999,10 @@
         <v>211</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E25" s="3">
         <v>200</v>
@@ -2008,10 +2014,10 @@
         <v>16</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>34</v>
@@ -2026,10 +2032,10 @@
         <v>212</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E26" s="3">
         <v>200</v>
@@ -2041,10 +2047,10 @@
         <v>16</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>34</v>
@@ -2059,10 +2065,10 @@
         <v>301</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E27" s="3">
         <v>300</v>
@@ -2074,10 +2080,10 @@
         <v>30</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>34</v>
@@ -2092,10 +2098,10 @@
         <v>302</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E28" s="3">
         <v>300</v>
@@ -2107,10 +2113,10 @@
         <v>30</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>34</v>
@@ -2125,10 +2131,10 @@
         <v>303</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E29" s="3">
         <v>300</v>
@@ -2140,10 +2146,10 @@
         <v>30</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>34</v>
@@ -2158,10 +2164,10 @@
         <v>304</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E30" s="3">
         <v>300</v>
@@ -2173,10 +2179,10 @@
         <v>30</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>34</v>
@@ -2191,10 +2197,10 @@
         <v>401</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E31" s="3">
         <v>300</v>
@@ -2206,13 +2212,13 @@
         <v>10</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>35</v>
@@ -2224,10 +2230,10 @@
         <v>402</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E32" s="3">
         <v>300</v>
@@ -2239,13 +2245,13 @@
         <v>10</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>35</v>
@@ -2256,10 +2262,10 @@
         <v>501</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E33" s="3">
         <v>1000</v>
@@ -2271,13 +2277,13 @@
         <v>-1</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>35</v>
@@ -2288,10 +2294,10 @@
         <v>502</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E34" s="3">
         <v>1000</v>
@@ -2303,13 +2309,13 @@
         <v>-1</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>35</v>
@@ -2320,10 +2326,10 @@
         <v>503</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E35" s="3">
         <v>1000</v>
@@ -2335,13 +2341,13 @@
         <v>-1</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>35</v>
@@ -2352,10 +2358,10 @@
         <v>504</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E36" s="3">
         <v>1000</v>
@@ -2367,13 +2373,13 @@
         <v>-1</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>35</v>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="62">
   <si>
     <t>##var</t>
   </si>
@@ -121,13 +121,13 @@
     <t>备注</t>
   </si>
   <si>
-    <t>小兔子</t>
+    <t>小体型怪</t>
   </si>
   <si>
     <t>Small</t>
   </si>
   <si>
-    <t>Meat:3|Bullet:0|ThreeKPCoin:0|Energy:2</t>
+    <t>Meat:5|Bullet:0|ThreeKPCoin:0|Energy:5</t>
   </si>
   <si>
     <t>Arts/Animals/Prefabs/pf_animal_forest_small_coin</t>
@@ -145,37 +145,40 @@
     <t>Arts/Animals/Prefabs/pf_animal_snow_small_coin02</t>
   </si>
   <si>
-    <t>中兔子</t>
+    <t>野猪</t>
   </si>
   <si>
     <t>Medium</t>
   </si>
   <si>
-    <t>Meat:6|Bullet:0|ThreeKPCoin:0|Energy:4</t>
+    <t>Meat:10|Bullet:0|ThreeKPCoin:0|Energy:10</t>
   </si>
   <si>
     <t>Arts/Animals/Prefabs/pf_animal_forest_medium_pig</t>
   </si>
   <si>
-    <t>大兔子</t>
+    <t>Meat:10|Bullet:0|ThreeKPCoin:0|Energy:20</t>
+  </si>
+  <si>
+    <t>大体型怪</t>
   </si>
   <si>
     <t>Large</t>
   </si>
   <si>
-    <t>Meat:20|Bullet:0|ThreeKPCoin:0|Energy:10</t>
+    <t>Meat:20|Bullet:0|ThreeKPCoin:0|Energy:20</t>
   </si>
   <si>
     <t>Arts/Animals/Prefabs/pf_animal_forest_large_coin</t>
   </si>
   <si>
-    <t>弹药兔子</t>
+    <t>弹药怪</t>
   </si>
   <si>
     <t>Bullet</t>
   </si>
   <si>
-    <t>Meat:20|Bullet:1|ThreeKPCoin:0|Energy:10</t>
+    <t>Meat:20|Bullet:1|ThreeKPCoin:0|Energy:20</t>
   </si>
   <si>
     <t>Arts/Animals/Prefabs/pf_animal_forest_special_bulletcoin</t>
@@ -184,13 +187,13 @@
     <t>Arts/Effects/Prefabs/FX_IPJSTX001</t>
   </si>
   <si>
-    <t>金币兔子</t>
+    <t>金币怪</t>
   </si>
   <si>
     <t>ThreeKPCoin</t>
   </si>
   <si>
-    <t>Meat:0|Bullet:0|ThreeKPCoin:10|Energy:10</t>
+    <t>Meat:10|Bullet:0|ThreeKPCoin:10|Energy:20</t>
   </si>
   <si>
     <t>Arts/Animals/Prefabs/pf_animal_forest_special_threekpcoin</t>
@@ -199,13 +202,13 @@
     <t>Arts/Effects/Prefabs/FX_IPJSTX002_1</t>
   </si>
   <si>
-    <t>超级大兔子</t>
+    <t>超级怪</t>
   </si>
   <si>
     <t>Boss</t>
   </si>
   <si>
-    <t>Meat:2000|Bullet:0|ThreeKPCoin:0|Energy:10</t>
+    <t>Meat:200|Bullet:0|ThreeKPCoin:0|Energy:0</t>
   </si>
   <si>
     <t>Arts/Animals/Prefabs/pf_animal_snow_boss_coin</t>
@@ -1351,7 +1354,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -1384,7 +1387,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -1417,7 +1420,7 @@
         <v>2</v>
       </c>
       <c r="G7" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -1450,7 +1453,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
@@ -1483,7 +1486,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -1516,7 +1519,7 @@
         <v>2</v>
       </c>
       <c r="G10" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -1549,7 +1552,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -1582,7 +1585,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -1615,7 +1618,7 @@
         <v>2</v>
       </c>
       <c r="G13" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -1648,7 +1651,7 @@
         <v>2</v>
       </c>
       <c r="G14" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -1675,13 +1678,13 @@
         <v>39</v>
       </c>
       <c r="E15" s="3">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F15" s="3">
         <v>1.5</v>
       </c>
       <c r="G15" s="3">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>40</v>
@@ -1708,13 +1711,13 @@
         <v>39</v>
       </c>
       <c r="E16" s="3">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F16" s="3">
         <v>1.5</v>
       </c>
       <c r="G16" s="3">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>40</v>
@@ -1741,13 +1744,13 @@
         <v>39</v>
       </c>
       <c r="E17" s="3">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F17" s="3">
         <v>1.5</v>
       </c>
       <c r="G17" s="3">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>40</v>
@@ -1774,13 +1777,13 @@
         <v>39</v>
       </c>
       <c r="E18" s="3">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F18" s="3">
         <v>1.5</v>
       </c>
       <c r="G18" s="3">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>40</v>
@@ -1807,13 +1810,13 @@
         <v>39</v>
       </c>
       <c r="E19" s="3">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F19" s="3">
         <v>1.5</v>
       </c>
       <c r="G19" s="3">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>40</v>
@@ -1840,13 +1843,13 @@
         <v>39</v>
       </c>
       <c r="E20" s="3">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F20" s="3">
         <v>1.5</v>
       </c>
       <c r="G20" s="3">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>40</v>
@@ -1873,13 +1876,13 @@
         <v>39</v>
       </c>
       <c r="E21" s="3">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F21" s="3">
         <v>1.5</v>
       </c>
       <c r="G21" s="3">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>40</v>
@@ -1906,13 +1909,13 @@
         <v>39</v>
       </c>
       <c r="E22" s="3">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F22" s="3">
         <v>1.5</v>
       </c>
       <c r="G22" s="3">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>40</v>
@@ -1939,13 +1942,13 @@
         <v>39</v>
       </c>
       <c r="E23" s="3">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F23" s="3">
         <v>1.5</v>
       </c>
       <c r="G23" s="3">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>40</v>
@@ -1972,13 +1975,13 @@
         <v>39</v>
       </c>
       <c r="E24" s="3">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F24" s="3">
         <v>1.5</v>
       </c>
       <c r="G24" s="3">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>40</v>
@@ -2005,13 +2008,13 @@
         <v>39</v>
       </c>
       <c r="E25" s="3">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F25" s="3">
         <v>1.5</v>
       </c>
       <c r="G25" s="3">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>40</v>
@@ -2038,16 +2041,16 @@
         <v>39</v>
       </c>
       <c r="E26" s="3">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F26" s="3">
         <v>1.5</v>
       </c>
       <c r="G26" s="3">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>41</v>
@@ -2065,25 +2068,25 @@
         <v>301</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E27" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F27" s="3">
         <v>1</v>
       </c>
       <c r="G27" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>34</v>
@@ -2098,25 +2101,25 @@
         <v>302</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E28" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F28" s="3">
         <v>1</v>
       </c>
       <c r="G28" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>34</v>
@@ -2131,25 +2134,25 @@
         <v>303</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E29" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F29" s="3">
         <v>1</v>
       </c>
       <c r="G29" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>34</v>
@@ -2164,25 +2167,25 @@
         <v>304</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E30" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F30" s="3">
         <v>1</v>
       </c>
       <c r="G30" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>34</v>
@@ -2197,13 +2200,13 @@
         <v>401</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E31" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F31" s="3">
         <v>1</v>
@@ -2212,13 +2215,13 @@
         <v>10</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>35</v>
@@ -2230,13 +2233,13 @@
         <v>402</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E32" s="3">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="F32" s="3">
         <v>1</v>
@@ -2245,13 +2248,13 @@
         <v>10</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>35</v>
@@ -2262,10 +2265,10 @@
         <v>501</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E33" s="3">
         <v>1000</v>
@@ -2277,13 +2280,13 @@
         <v>-1</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>35</v>
@@ -2294,10 +2297,10 @@
         <v>502</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E34" s="3">
         <v>1000</v>
@@ -2309,13 +2312,13 @@
         <v>-1</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>35</v>
@@ -2326,10 +2329,10 @@
         <v>503</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E35" s="3">
         <v>1000</v>
@@ -2341,13 +2344,13 @@
         <v>-1</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>35</v>
@@ -2358,10 +2361,10 @@
         <v>504</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E36" s="3">
         <v>1000</v>
@@ -2373,13 +2376,13 @@
         <v>-1</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>35</v>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -130,7 +130,7 @@
     <t>Meat:5|Bullet:0|ThreeKPCoin:0|Energy:5</t>
   </si>
   <si>
-    <t>Arts/Animals/Prefabs/pf_animal_forest_small_coin</t>
+    <t>Arts/Animals/Prefabs/pf_animal_forest_small_yeji</t>
   </si>
   <si>
     <t>Arts/Effects/Prefabs/FX_JXTX001_01</t>
@@ -139,10 +139,10 @@
     <t>/</t>
   </si>
   <si>
-    <t>Arts/Animals/Prefabs/pf_animal_snow_small_coin01</t>
-  </si>
-  <si>
-    <t>Arts/Animals/Prefabs/pf_animal_snow_small_coin02</t>
+    <t>Arts/Animals/Prefabs/pf_animal_snow_small_baozi</t>
+  </si>
+  <si>
+    <t>Arts/Animals/Prefabs/pf_animal_snow_small_yeji</t>
   </si>
   <si>
     <t>野猪</t>
@@ -154,7 +154,7 @@
     <t>Meat:10|Bullet:0|ThreeKPCoin:0|Energy:10</t>
   </si>
   <si>
-    <t>Arts/Animals/Prefabs/pf_animal_forest_medium_pig</t>
+    <t>Arts/Animals/Prefabs/pf_animal_forest_medium_yezhu</t>
   </si>
   <si>
     <t>Meat:10|Bullet:0|ThreeKPCoin:0|Energy:20</t>
@@ -169,7 +169,7 @@
     <t>Meat:20|Bullet:0|ThreeKPCoin:0|Energy:20</t>
   </si>
   <si>
-    <t>Arts/Animals/Prefabs/pf_animal_forest_large_coin</t>
+    <t>Arts/Animals/Prefabs/pf_animal_forest_large_baozi</t>
   </si>
   <si>
     <t>弹药怪</t>
@@ -211,7 +211,7 @@
     <t>Meat:200|Bullet:0|ThreeKPCoin:0|Energy:0</t>
   </si>
   <si>
-    <t>Arts/Animals/Prefabs/pf_animal_snow_boss_coin</t>
+    <t>Arts/Animals/Prefabs/pf_animal_snow_boss_yezhu</t>
   </si>
   <si>
     <t>Arts/Effects/Prefabs/FX_JXTX001_03</t>
@@ -2077,7 +2077,7 @@
         <v>400</v>
       </c>
       <c r="F27" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G27" s="3">
         <v>36</v>
@@ -2110,7 +2110,7 @@
         <v>400</v>
       </c>
       <c r="F28" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G28" s="3">
         <v>36</v>
@@ -2143,7 +2143,7 @@
         <v>400</v>
       </c>
       <c r="F29" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G29" s="3">
         <v>36</v>
@@ -2176,7 +2176,7 @@
         <v>400</v>
       </c>
       <c r="F30" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G30" s="3">
         <v>36</v>
@@ -2271,7 +2271,7 @@
         <v>58</v>
       </c>
       <c r="E33" s="3">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F33" s="3">
         <v>6</v>
@@ -2303,7 +2303,7 @@
         <v>58</v>
       </c>
       <c r="E34" s="3">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F34" s="3">
         <v>6</v>
@@ -2335,7 +2335,7 @@
         <v>58</v>
       </c>
       <c r="E35" s="3">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F35" s="3">
         <v>6</v>
@@ -2367,7 +2367,7 @@
         <v>58</v>
       </c>
       <c r="E36" s="3">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F36" s="3">
         <v>6</v>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -130,19 +130,19 @@
     <t>Meat:5|Bullet:0|ThreeKPCoin:0|Energy:5</t>
   </si>
   <si>
-    <t>Arts/Animals/Prefabs/pf_animal_forest_small_yeji</t>
-  </si>
-  <si>
-    <t>Arts/Effects/Prefabs/FX_JXTX001_01</t>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_small_yeji</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Prefabs/Effects/FX_JXTX001_01</t>
   </si>
   <si>
     <t>/</t>
   </si>
   <si>
-    <t>Arts/Animals/Prefabs/pf_animal_snow_small_baozi</t>
-  </si>
-  <si>
-    <t>Arts/Animals/Prefabs/pf_animal_snow_small_yeji</t>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_small_yeji</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_small_baozi</t>
   </si>
   <si>
     <t>野猪</t>
@@ -154,7 +154,7 @@
     <t>Meat:10|Bullet:0|ThreeKPCoin:0|Energy:10</t>
   </si>
   <si>
-    <t>Arts/Animals/Prefabs/pf_animal_forest_medium_yezhu</t>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_medium_yezhu</t>
   </si>
   <si>
     <t>Meat:10|Bullet:0|ThreeKPCoin:0|Energy:20</t>
@@ -169,7 +169,7 @@
     <t>Meat:20|Bullet:0|ThreeKPCoin:0|Energy:20</t>
   </si>
   <si>
-    <t>Arts/Animals/Prefabs/pf_animal_forest_large_baozi</t>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_large_baozi</t>
   </si>
   <si>
     <t>弹药怪</t>
@@ -181,10 +181,10 @@
     <t>Meat:20|Bullet:1|ThreeKPCoin:0|Energy:20</t>
   </si>
   <si>
-    <t>Arts/Animals/Prefabs/pf_animal_forest_special_bulletcoin</t>
-  </si>
-  <si>
-    <t>Arts/Effects/Prefabs/FX_IPJSTX001</t>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_special_bulletcoin</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Prefabs/Effects/FX_IPJSTX001</t>
   </si>
   <si>
     <t>金币怪</t>
@@ -196,10 +196,10 @@
     <t>Meat:10|Bullet:0|ThreeKPCoin:10|Energy:20</t>
   </si>
   <si>
-    <t>Arts/Animals/Prefabs/pf_animal_forest_special_threekpcoin</t>
-  </si>
-  <si>
-    <t>Arts/Effects/Prefabs/FX_IPJSTX002_1</t>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_special_threekpcoin</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Prefabs/Effects/FX_IPJSTX002_1</t>
   </si>
   <si>
     <t>超级怪</t>
@@ -211,10 +211,10 @@
     <t>Meat:200|Bullet:0|ThreeKPCoin:0|Energy:0</t>
   </si>
   <si>
-    <t>Arts/Animals/Prefabs/pf_animal_snow_boss_yezhu</t>
-  </si>
-  <si>
-    <t>Arts/Effects/Prefabs/FX_JXTX001_03</t>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_boss_yezhu</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Prefabs/Effects/FX_JXTX001_03</t>
   </si>
 </sst>
 </file>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="72">
   <si>
     <t>##var</t>
   </si>
@@ -58,7 +58,10 @@
     <t>PrefabResourcePath</t>
   </si>
   <si>
-    <t>EffectPrefabPath</t>
+    <t>EffectPrefabResourcePath</t>
+  </si>
+  <si>
+    <t>IconResourcePath</t>
   </si>
   <si>
     <t>Comment</t>
@@ -115,7 +118,10 @@
     <t>预制体资源路径</t>
   </si>
   <si>
-    <t>特效预制体路径</t>
+    <t>特效预制体资源路径</t>
+  </si>
+  <si>
+    <t>图标资源路径</t>
   </si>
   <si>
     <t>备注</t>
@@ -136,9 +142,18 @@
     <t>Assets/Arts/Prefabs/Effects/FX_JXTX001_01</t>
   </si>
   <si>
+    <t>Assets/Arts/UI/Sprites/Gameplay/Animals/Skull_01</t>
+  </si>
+  <si>
     <t>/</t>
   </si>
   <si>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_small_tuzi</t>
+  </si>
+  <si>
+    <t>Assets/Arts/UI/Sprites/Gameplay/Animals/Skull_02</t>
+  </si>
+  <si>
     <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_small_yeji</t>
   </si>
   <si>
@@ -157,6 +172,18 @@
     <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_medium_yezhu</t>
   </si>
   <si>
+    <t>Assets/Arts/UI/Sprites/Gameplay/Animals/Skull_03</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_medium_lu</t>
+  </si>
+  <si>
+    <t>Assets/Arts/UI/Sprites/Gameplay/Animals/Skull_04</t>
+  </si>
+  <si>
+    <t>Assets/Arts/UI/Sprites/Gameplay/Animals/Skull_05</t>
+  </si>
+  <si>
     <t>Meat:10|Bullet:0|ThreeKPCoin:0|Energy:20</t>
   </si>
   <si>
@@ -172,6 +199,9 @@
     <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_large_baozi</t>
   </si>
   <si>
+    <t>Assets/Arts/UI/Sprites/Gameplay/Animals/Skull_06</t>
+  </si>
+  <si>
     <t>弹药怪</t>
   </si>
   <si>
@@ -181,7 +211,7 @@
     <t>Meat:20|Bullet:1|ThreeKPCoin:0|Energy:20</t>
   </si>
   <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_special_bulletcoin</t>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_special_bulletcoin</t>
   </si>
   <si>
     <t>Assets/Arts/Prefabs/Effects/FX_IPJSTX001</t>
@@ -196,7 +226,7 @@
     <t>Meat:10|Bullet:0|ThreeKPCoin:10|Energy:20</t>
   </si>
   <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_special_threekpcoin</t>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_special_threekpcoin</t>
   </si>
   <si>
     <t>Assets/Arts/Prefabs/Effects/FX_IPJSTX002_1</t>
@@ -1184,7 +1214,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="3" width="28.625" customWidth="1"/>
@@ -1193,10 +1223,11 @@
     <col min="8" max="8" width="62.7833333333333" customWidth="1"/>
     <col min="9" max="9" width="78.625" customWidth="1"/>
     <col min="10" max="10" width="48.625" customWidth="1"/>
-    <col min="11" max="11" width="28.625" customWidth="1"/>
+    <col min="11" max="11" width="76.625" customWidth="1"/>
+    <col min="12" max="12" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:11">
+    <row r="1" ht="28" customHeight="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1230,122 +1261,134 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" ht="28" customHeight="1" spans="1:11">
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="J2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:11">
+        <v>14</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:11">
+        <v>30</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1" spans="1:12">
       <c r="A5" s="3"/>
       <c r="B5" s="3">
         <v>101</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5" s="3">
         <v>100</v>
@@ -1357,28 +1400,31 @@
         <v>20</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:11">
+        <v>37</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:12">
       <c r="A6" s="3"/>
       <c r="B6" s="3">
         <v>102</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6" s="3">
         <v>100</v>
@@ -1390,28 +1436,31 @@
         <v>20</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:11">
+        <v>40</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:12">
       <c r="A7" s="3"/>
       <c r="B7" s="3">
         <v>103</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E7" s="3">
         <v>100</v>
@@ -1423,28 +1472,31 @@
         <v>20</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:11">
+        <v>37</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1" spans="1:12">
       <c r="A8" s="3"/>
       <c r="B8" s="3">
         <v>104</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
@@ -1456,28 +1508,31 @@
         <v>20</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:11">
+        <v>40</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1" spans="1:12">
       <c r="A9" s="3"/>
       <c r="B9" s="3">
         <v>105</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E9" s="3">
         <v>100</v>
@@ -1489,28 +1544,31 @@
         <v>20</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:11">
+        <v>37</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:12">
       <c r="A10" s="3"/>
       <c r="B10" s="3">
         <v>106</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E10" s="3">
         <v>100</v>
@@ -1522,28 +1580,31 @@
         <v>20</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:11">
+        <v>40</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:12">
       <c r="A11" s="3"/>
       <c r="B11" s="3">
         <v>107</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E11" s="3">
         <v>100</v>
@@ -1555,28 +1616,31 @@
         <v>20</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:11">
+        <v>37</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:12">
       <c r="A12" s="3"/>
       <c r="B12" s="3">
         <v>108</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E12" s="3">
         <v>100</v>
@@ -1588,28 +1652,31 @@
         <v>20</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:11">
+        <v>40</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:12">
       <c r="A13" s="3"/>
       <c r="B13" s="3">
         <v>109</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E13" s="3">
         <v>100</v>
@@ -1621,28 +1688,31 @@
         <v>20</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="1:11">
+        <v>37</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1" spans="1:12">
       <c r="A14" s="3"/>
       <c r="B14" s="3">
         <v>110</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E14" s="3">
         <v>100</v>
@@ -1654,28 +1724,31 @@
         <v>20</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:11">
+        <v>40</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1" spans="1:12">
       <c r="A15" s="3"/>
       <c r="B15" s="3">
         <v>201</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E15" s="3">
         <v>250</v>
@@ -1687,61 +1760,67 @@
         <v>28</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1" spans="1:11">
+        <v>47</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:12">
       <c r="A16" s="3"/>
       <c r="B16" s="3">
         <v>202</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E16" s="3">
         <v>250</v>
       </c>
       <c r="F16" s="3">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G16" s="3">
         <v>28</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1" spans="1:11">
+        <v>49</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="1:12">
       <c r="A17" s="3"/>
       <c r="B17" s="3">
         <v>203</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E17" s="3">
         <v>250</v>
@@ -1753,28 +1832,31 @@
         <v>28</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1" spans="1:11">
+        <v>50</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1" spans="1:12">
       <c r="A18" s="3"/>
       <c r="B18" s="3">
         <v>204</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E18" s="3">
         <v>250</v>
@@ -1786,61 +1868,67 @@
         <v>28</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:11">
+        <v>47</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1" spans="1:12">
       <c r="A19" s="3"/>
       <c r="B19" s="3">
         <v>205</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E19" s="3">
         <v>250</v>
       </c>
       <c r="F19" s="3">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G19" s="3">
         <v>28</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="1:11">
+        <v>49</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1" spans="1:12">
       <c r="A20" s="3"/>
       <c r="B20" s="3">
         <v>206</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E20" s="3">
         <v>250</v>
@@ -1852,28 +1940,31 @@
         <v>28</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1" spans="1:11">
+        <v>50</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1" spans="1:12">
       <c r="A21" s="3"/>
       <c r="B21" s="3">
         <v>207</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E21" s="3">
         <v>250</v>
@@ -1885,61 +1976,67 @@
         <v>28</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1" spans="1:11">
+        <v>47</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1" spans="1:12">
       <c r="A22" s="3"/>
       <c r="B22" s="3">
         <v>208</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E22" s="3">
         <v>250</v>
       </c>
       <c r="F22" s="3">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G22" s="3">
         <v>28</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1" spans="1:11">
+        <v>49</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:12">
       <c r="A23" s="3"/>
       <c r="B23" s="3">
         <v>209</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E23" s="3">
         <v>250</v>
@@ -1951,28 +2048,31 @@
         <v>28</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1" spans="1:11">
+        <v>50</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1" spans="1:12">
       <c r="A24" s="3"/>
       <c r="B24" s="3">
         <v>210</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E24" s="3">
         <v>250</v>
@@ -1984,61 +2084,67 @@
         <v>28</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1" spans="1:11">
+        <v>47</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1" spans="1:12">
       <c r="A25" s="3"/>
       <c r="B25" s="3">
         <v>211</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E25" s="3">
         <v>250</v>
       </c>
       <c r="F25" s="3">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G25" s="3">
         <v>28</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1" spans="1:11">
+        <v>49</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1" spans="1:12">
       <c r="A26" s="3"/>
       <c r="B26" s="3">
         <v>212</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E26" s="3">
         <v>250</v>
@@ -2050,28 +2156,31 @@
         <v>28</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1" spans="1:11">
+        <v>50</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1" spans="1:12">
       <c r="A27" s="3"/>
       <c r="B27" s="3">
         <v>301</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E27" s="3">
         <v>400</v>
@@ -2083,28 +2192,31 @@
         <v>36</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1" spans="1:11">
+        <v>56</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1" spans="1:12">
       <c r="A28" s="3"/>
       <c r="B28" s="3">
         <v>302</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E28" s="3">
         <v>400</v>
@@ -2116,28 +2228,31 @@
         <v>36</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1" spans="1:11">
+        <v>56</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1" spans="1:12">
       <c r="A29" s="3"/>
       <c r="B29" s="3">
         <v>303</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E29" s="3">
         <v>400</v>
@@ -2149,28 +2264,31 @@
         <v>36</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1" spans="1:11">
+        <v>56</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1" spans="1:12">
       <c r="A30" s="3"/>
       <c r="B30" s="3">
         <v>304</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E30" s="3">
         <v>400</v>
@@ -2182,28 +2300,31 @@
         <v>36</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1" spans="1:11">
+        <v>56</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1" spans="1:12">
       <c r="A31" s="3"/>
       <c r="B31" s="3">
         <v>401</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E31" s="3">
         <v>500</v>
@@ -2215,28 +2336,31 @@
         <v>10</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1" spans="1:11">
+        <v>38</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1" spans="1:12">
       <c r="A32" s="3"/>
       <c r="B32" s="3">
         <v>402</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E32" s="3">
         <v>250</v>
@@ -2248,27 +2372,30 @@
         <v>10</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1" spans="2:11">
+        <v>38</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1" spans="2:12">
       <c r="B33" s="3">
         <v>501</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E33" s="3">
         <v>2000</v>
@@ -2280,27 +2407,30 @@
         <v>-1</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1" spans="2:11">
+        <v>38</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1" spans="2:12">
       <c r="B34" s="3">
         <v>502</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E34" s="3">
         <v>2000</v>
@@ -2312,27 +2442,30 @@
         <v>-1</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1" spans="2:11">
+        <v>38</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1" spans="2:12">
       <c r="B35" s="3">
         <v>503</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E35" s="3">
         <v>2000</v>
@@ -2344,27 +2477,30 @@
         <v>-1</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1" spans="2:11">
+        <v>38</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1" spans="2:12">
       <c r="B36" s="3">
         <v>504</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E36" s="3">
         <v>2000</v>
@@ -2376,16 +2512,19 @@
         <v>-1</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -208,7 +208,7 @@
     <t>Bullet</t>
   </si>
   <si>
-    <t>Meat:20|Bullet:1|ThreeKPCoin:0|Energy:20</t>
+    <t>Meat:0|Bullet:1|ThreeKPCoin:0|Energy:20</t>
   </si>
   <si>
     <t>Assets/Arts/Prefabs/Animals/pf_animal_special_bulletcoin</t>
@@ -223,7 +223,7 @@
     <t>ThreeKPCoin</t>
   </si>
   <si>
-    <t>Meat:10|Bullet:0|ThreeKPCoin:10|Energy:20</t>
+    <t>Meat:0|Bullet:0|ThreeKPCoin:10|Energy:20</t>
   </si>
   <si>
     <t>Assets/Arts/Prefabs/Animals/pf_animal_special_threekpcoin</t>
@@ -1397,7 +1397,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>34</v>
@@ -1433,7 +1433,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>34</v>
@@ -1469,7 +1469,7 @@
         <v>2</v>
       </c>
       <c r="G7" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>34</v>
@@ -1505,7 +1505,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>34</v>
@@ -1541,7 +1541,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>34</v>
@@ -1577,7 +1577,7 @@
         <v>2</v>
       </c>
       <c r="G10" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>34</v>
@@ -1613,7 +1613,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>34</v>
@@ -1649,7 +1649,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>34</v>
@@ -1685,7 +1685,7 @@
         <v>2</v>
       </c>
       <c r="G13" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>34</v>
@@ -1721,7 +1721,7 @@
         <v>2</v>
       </c>
       <c r="G14" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>34</v>
@@ -1751,13 +1751,13 @@
         <v>44</v>
       </c>
       <c r="E15" s="3">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F15" s="3">
         <v>1.5</v>
       </c>
       <c r="G15" s="3">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>45</v>
@@ -1787,13 +1787,13 @@
         <v>44</v>
       </c>
       <c r="E16" s="3">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F16" s="3">
         <v>2.5</v>
       </c>
       <c r="G16" s="3">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>45</v>
@@ -1823,13 +1823,13 @@
         <v>44</v>
       </c>
       <c r="E17" s="3">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F17" s="3">
         <v>1.5</v>
       </c>
       <c r="G17" s="3">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>45</v>
@@ -1859,13 +1859,13 @@
         <v>44</v>
       </c>
       <c r="E18" s="3">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F18" s="3">
         <v>1.5</v>
       </c>
       <c r="G18" s="3">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>45</v>
@@ -1895,13 +1895,13 @@
         <v>44</v>
       </c>
       <c r="E19" s="3">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F19" s="3">
         <v>2.5</v>
       </c>
       <c r="G19" s="3">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>45</v>
@@ -1931,13 +1931,13 @@
         <v>44</v>
       </c>
       <c r="E20" s="3">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F20" s="3">
         <v>1.5</v>
       </c>
       <c r="G20" s="3">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>45</v>
@@ -1967,13 +1967,13 @@
         <v>44</v>
       </c>
       <c r="E21" s="3">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F21" s="3">
         <v>1.5</v>
       </c>
       <c r="G21" s="3">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>45</v>
@@ -2003,13 +2003,13 @@
         <v>44</v>
       </c>
       <c r="E22" s="3">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F22" s="3">
         <v>2.5</v>
       </c>
       <c r="G22" s="3">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>45</v>
@@ -2039,13 +2039,13 @@
         <v>44</v>
       </c>
       <c r="E23" s="3">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F23" s="3">
         <v>1.5</v>
       </c>
       <c r="G23" s="3">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>45</v>
@@ -2075,13 +2075,13 @@
         <v>44</v>
       </c>
       <c r="E24" s="3">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F24" s="3">
         <v>1.5</v>
       </c>
       <c r="G24" s="3">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>45</v>
@@ -2111,13 +2111,13 @@
         <v>44</v>
       </c>
       <c r="E25" s="3">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F25" s="3">
         <v>2.5</v>
       </c>
       <c r="G25" s="3">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>45</v>
@@ -2147,13 +2147,13 @@
         <v>44</v>
       </c>
       <c r="E26" s="3">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F26" s="3">
         <v>1.5</v>
       </c>
       <c r="G26" s="3">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>51</v>
@@ -2183,13 +2183,13 @@
         <v>53</v>
       </c>
       <c r="E27" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F27" s="3">
         <v>4</v>
       </c>
       <c r="G27" s="3">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>54</v>
@@ -2219,13 +2219,13 @@
         <v>53</v>
       </c>
       <c r="E28" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F28" s="3">
         <v>4</v>
       </c>
       <c r="G28" s="3">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>51</v>
@@ -2255,13 +2255,13 @@
         <v>53</v>
       </c>
       <c r="E29" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F29" s="3">
         <v>4</v>
       </c>
       <c r="G29" s="3">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>54</v>
@@ -2291,13 +2291,13 @@
         <v>53</v>
       </c>
       <c r="E30" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F30" s="3">
         <v>4</v>
       </c>
       <c r="G30" s="3">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>51</v>
@@ -2333,7 +2333,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>59</v>
@@ -2363,7 +2363,7 @@
         <v>63</v>
       </c>
       <c r="E32" s="3">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F32" s="3">
         <v>1</v>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2398,7 +2398,7 @@
         <v>68</v>
       </c>
       <c r="E33" s="3">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="F33" s="3">
         <v>6</v>
@@ -2433,7 +2433,7 @@
         <v>68</v>
       </c>
       <c r="E34" s="3">
-        <v>2000</v>
+        <v>101</v>
       </c>
       <c r="F34" s="3">
         <v>6</v>
@@ -2468,7 +2468,7 @@
         <v>68</v>
       </c>
       <c r="E35" s="3">
-        <v>2000</v>
+        <v>102</v>
       </c>
       <c r="F35" s="3">
         <v>6</v>
@@ -2503,7 +2503,7 @@
         <v>68</v>
       </c>
       <c r="E36" s="3">
-        <v>2000</v>
+        <v>103</v>
       </c>
       <c r="F36" s="3">
         <v>6</v>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2330,7 +2330,7 @@
         <v>500</v>
       </c>
       <c r="F31" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="3">
         <v>20</v>
@@ -2366,7 +2366,7 @@
         <v>300</v>
       </c>
       <c r="F32" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G32" s="3">
         <v>10</v>
@@ -2433,7 +2433,7 @@
         <v>68</v>
       </c>
       <c r="E34" s="3">
-        <v>101</v>
+        <v>2000</v>
       </c>
       <c r="F34" s="3">
         <v>6</v>
@@ -2468,7 +2468,7 @@
         <v>68</v>
       </c>
       <c r="E35" s="3">
-        <v>102</v>
+        <v>2000</v>
       </c>
       <c r="F35" s="3">
         <v>6</v>
@@ -2503,7 +2503,7 @@
         <v>68</v>
       </c>
       <c r="E36" s="3">
-        <v>103</v>
+        <v>2000</v>
       </c>
       <c r="F36" s="3">
         <v>6</v>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2330,7 +2330,7 @@
         <v>500</v>
       </c>
       <c r="F31" s="3">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G31" s="3">
         <v>20</v>
@@ -2366,7 +2366,7 @@
         <v>300</v>
       </c>
       <c r="F32" s="3">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G32" s="3">
         <v>10</v>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="66">
   <si>
     <t>##var</t>
   </si>
@@ -151,9 +151,6 @@
     <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_small_tuzi</t>
   </si>
   <si>
-    <t>Assets/Arts/UI/Sprites/Gameplay/Animals/Skull_02</t>
-  </si>
-  <si>
     <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_small_yeji</t>
   </si>
   <si>
@@ -172,18 +169,9 @@
     <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_medium_yezhu</t>
   </si>
   <si>
-    <t>Assets/Arts/UI/Sprites/Gameplay/Animals/Skull_03</t>
-  </si>
-  <si>
     <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_medium_lu</t>
   </si>
   <si>
-    <t>Assets/Arts/UI/Sprites/Gameplay/Animals/Skull_04</t>
-  </si>
-  <si>
-    <t>Assets/Arts/UI/Sprites/Gameplay/Animals/Skull_05</t>
-  </si>
-  <si>
     <t>Meat:10|Bullet:0|ThreeKPCoin:0|Energy:20</t>
   </si>
   <si>
@@ -194,12 +182,6 @@
   </si>
   <si>
     <t>Meat:20|Bullet:0|ThreeKPCoin:0|Energy:20</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_large_baozi</t>
-  </si>
-  <si>
-    <t>Assets/Arts/UI/Sprites/Gameplay/Animals/Skull_06</t>
   </si>
   <si>
     <t>弹药怪</t>
@@ -1445,7 +1427,7 @@
         <v>36</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>38</v>
@@ -1517,7 +1499,7 @@
         <v>36</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>38</v>
@@ -1589,7 +1571,7 @@
         <v>36</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>38</v>
@@ -1661,7 +1643,7 @@
         <v>36</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>38</v>
@@ -1691,7 +1673,7 @@
         <v>34</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>36</v>
@@ -1727,13 +1709,13 @@
         <v>34</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>38</v>
@@ -1745,10 +1727,10 @@
         <v>201</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="E15" s="3">
         <v>300</v>
@@ -1760,16 +1742,16 @@
         <v>12</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>38</v>
@@ -1781,10 +1763,10 @@
         <v>202</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="E16" s="3">
         <v>300</v>
@@ -1796,16 +1778,16 @@
         <v>12</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>38</v>
@@ -1817,10 +1799,10 @@
         <v>203</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="E17" s="3">
         <v>300</v>
@@ -1832,16 +1814,16 @@
         <v>12</v>
       </c>
       <c r="H17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>38</v>
@@ -1853,10 +1835,10 @@
         <v>204</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="E18" s="3">
         <v>300</v>
@@ -1868,16 +1850,16 @@
         <v>12</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>38</v>
@@ -1889,10 +1871,10 @@
         <v>205</v>
       </c>
       <c r="C19" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="E19" s="3">
         <v>300</v>
@@ -1904,16 +1886,16 @@
         <v>12</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>38</v>
@@ -1925,10 +1907,10 @@
         <v>206</v>
       </c>
       <c r="C20" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="E20" s="3">
         <v>300</v>
@@ -1940,16 +1922,16 @@
         <v>12</v>
       </c>
       <c r="H20" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>38</v>
@@ -1961,10 +1943,10 @@
         <v>207</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="E21" s="3">
         <v>300</v>
@@ -1976,16 +1958,16 @@
         <v>12</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>38</v>
@@ -1997,10 +1979,10 @@
         <v>208</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="E22" s="3">
         <v>300</v>
@@ -2012,16 +1994,16 @@
         <v>12</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>38</v>
@@ -2033,10 +2015,10 @@
         <v>209</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="E23" s="3">
         <v>300</v>
@@ -2048,16 +2030,16 @@
         <v>12</v>
       </c>
       <c r="H23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>38</v>
@@ -2069,10 +2051,10 @@
         <v>210</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="E24" s="3">
         <v>300</v>
@@ -2084,16 +2066,16 @@
         <v>12</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>38</v>
@@ -2105,10 +2087,10 @@
         <v>211</v>
       </c>
       <c r="C25" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="E25" s="3">
         <v>300</v>
@@ -2120,16 +2102,16 @@
         <v>12</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>38</v>
@@ -2141,10 +2123,10 @@
         <v>212</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="E26" s="3">
         <v>300</v>
@@ -2156,16 +2138,16 @@
         <v>12</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>38</v>
@@ -2177,10 +2159,10 @@
         <v>301</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E27" s="3">
         <v>500</v>
@@ -2192,16 +2174,16 @@
         <v>4</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>38</v>
@@ -2213,10 +2195,10 @@
         <v>302</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E28" s="3">
         <v>500</v>
@@ -2228,16 +2210,16 @@
         <v>4</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>38</v>
@@ -2249,10 +2231,10 @@
         <v>303</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E29" s="3">
         <v>500</v>
@@ -2264,16 +2246,16 @@
         <v>4</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>38</v>
@@ -2285,10 +2267,10 @@
         <v>304</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E30" s="3">
         <v>500</v>
@@ -2300,16 +2282,16 @@
         <v>4</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>38</v>
@@ -2321,10 +2303,10 @@
         <v>401</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E31" s="3">
         <v>500</v>
@@ -2336,13 +2318,13 @@
         <v>20</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>38</v>
@@ -2357,10 +2339,10 @@
         <v>402</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E32" s="3">
         <v>300</v>
@@ -2372,13 +2354,13 @@
         <v>10</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>38</v>
@@ -2392,10 +2374,10 @@
         <v>501</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E33" s="3">
         <v>100</v>
@@ -2407,13 +2389,13 @@
         <v>-1</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>38</v>
@@ -2427,10 +2409,10 @@
         <v>502</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E34" s="3">
         <v>2000</v>
@@ -2442,13 +2424,13 @@
         <v>-1</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>38</v>
@@ -2462,10 +2444,10 @@
         <v>503</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E35" s="3">
         <v>2000</v>
@@ -2477,13 +2459,13 @@
         <v>-1</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>38</v>
@@ -2497,10 +2479,10 @@
         <v>504</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E36" s="3">
         <v>2000</v>
@@ -2512,13 +2494,13 @@
         <v>-1</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>38</v>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="79">
   <si>
     <t>##var</t>
   </si>
@@ -58,7 +58,7 @@
     <t>PrefabResourcePath</t>
   </si>
   <si>
-    <t>EffectPrefabResourcePath</t>
+    <t>DropMeatEffectID</t>
   </si>
   <si>
     <t>IconResourcePath</t>
@@ -85,6 +85,9 @@
     <t>(map#sep=:|),HuntingConfig.Enum.EDropType,int</t>
   </si>
   <si>
+    <t>(array#sep=,),int</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -118,7 +121,7 @@
     <t>预制体资源路径</t>
   </si>
   <si>
-    <t>特效预制体资源路径</t>
+    <t>掉落肉特效ID</t>
   </si>
   <si>
     <t>图标资源路径</t>
@@ -127,63 +130,87 @@
     <t>备注</t>
   </si>
   <si>
+    <t>野鸡</t>
+  </si>
+  <si>
+    <t>Small</t>
+  </si>
+  <si>
+    <t>Meat:5|Bullet:0|ThreeKPCoin:0|Energy:5</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_small_yeji</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>Assets/Arts/UI/Sprites/Gameplay/Animals/Skull_01</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>兔子</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_small_tuzi</t>
+  </si>
+  <si>
     <t>小体型怪</t>
   </si>
   <si>
-    <t>Small</t>
-  </si>
-  <si>
-    <t>Meat:5|Bullet:0|ThreeKPCoin:0|Energy:5</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_small_yeji</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Prefabs/Effects/FX_JXTX001_01</t>
-  </si>
-  <si>
-    <t>Assets/Arts/UI/Sprites/Gameplay/Animals/Skull_01</t>
-  </si>
-  <si>
-    <t>/</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_small_tuzi</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_small_yeji</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_small_baozi</t>
+    <t>白狐</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_small_baihu</t>
+  </si>
+  <si>
+    <t>9,16</t>
+  </si>
+  <si>
+    <t>企鹅</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_small_qie</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Meat:10|Bullet:0|ThreeKPCoin:0|Energy:10</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_medium_yezhu</t>
+  </si>
+  <si>
+    <t>鹿</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_medium_lu</t>
   </si>
   <si>
     <t>野猪</t>
   </si>
   <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Meat:10|Bullet:0|ThreeKPCoin:0|Energy:10</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_medium_yezhu</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_medium_lu</t>
+    <t>中体型怪</t>
   </si>
   <si>
     <t>Meat:10|Bullet:0|ThreeKPCoin:0|Energy:20</t>
   </si>
   <si>
+    <t>豹子</t>
+  </si>
+  <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>Meat:20|Bullet:0|ThreeKPCoin:0|Energy:20</t>
+  </si>
+  <si>
     <t>大体型怪</t>
   </si>
   <si>
-    <t>Large</t>
-  </si>
-  <si>
-    <t>Meat:20|Bullet:0|ThreeKPCoin:0|Energy:20</t>
-  </si>
-  <si>
     <t>弹药怪</t>
   </si>
   <si>
@@ -196,9 +223,6 @@
     <t>Assets/Arts/Prefabs/Animals/pf_animal_special_bulletcoin</t>
   </si>
   <si>
-    <t>Assets/Arts/Prefabs/Effects/FX_IPJSTX001</t>
-  </si>
-  <si>
     <t>金币怪</t>
   </si>
   <si>
@@ -211,10 +235,10 @@
     <t>Assets/Arts/Prefabs/Animals/pf_animal_special_threekpcoin</t>
   </si>
   <si>
-    <t>Assets/Arts/Prefabs/Effects/FX_IPJSTX002_1</t>
-  </si>
-  <si>
-    <t>超级怪</t>
+    <t>101,102,103,104</t>
+  </si>
+  <si>
+    <t>雪猩猩</t>
   </si>
   <si>
     <t>Boss</t>
@@ -223,10 +247,25 @@
     <t>Meat:200|Bullet:0|ThreeKPCoin:0|Energy:0</t>
   </si>
   <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_boss_yezhu</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Prefabs/Effects/FX_JXTX001_03</t>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_boss_xuexingxing</t>
+  </si>
+  <si>
+    <t>猛犸象</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_boss_mengmaxiang</t>
+  </si>
+  <si>
+    <t>三角龙</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_boss_sanjiaolong</t>
+  </si>
+  <si>
+    <t>北极熊</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_boss_beijixiong</t>
   </si>
 </sst>
 </file>
@@ -869,7 +908,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -883,6 +922,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1204,7 +1246,7 @@
     <col min="5" max="7" width="28.625" customWidth="1"/>
     <col min="8" max="8" width="62.7833333333333" customWidth="1"/>
     <col min="9" max="9" width="78.625" customWidth="1"/>
-    <col min="10" max="10" width="48.625" customWidth="1"/>
+    <col min="10" max="10" width="28.625" customWidth="1"/>
     <col min="11" max="11" width="76.625" customWidth="1"/>
     <col min="12" max="12" width="28.625" customWidth="1"/>
   </cols>
@@ -1276,7 +1318,7 @@
         <v>14</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>14</v>
@@ -1287,78 +1329,78 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:12">
@@ -1367,10 +1409,10 @@
         <v>101</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5" s="3">
         <v>100</v>
@@ -1382,19 +1424,19 @@
         <v>8</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:12">
@@ -1403,10 +1445,10 @@
         <v>102</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6" s="3">
         <v>100</v>
@@ -1418,19 +1460,19 @@
         <v>8</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:12">
@@ -1439,10 +1481,10 @@
         <v>103</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7" s="3">
         <v>100</v>
@@ -1454,19 +1496,19 @@
         <v>8</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:12">
@@ -1475,10 +1517,10 @@
         <v>104</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
@@ -1490,19 +1532,19 @@
         <v>8</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:12">
@@ -1511,10 +1553,10 @@
         <v>105</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E9" s="3">
         <v>100</v>
@@ -1526,19 +1568,19 @@
         <v>8</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:12">
@@ -1547,10 +1589,10 @@
         <v>106</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E10" s="3">
         <v>100</v>
@@ -1562,19 +1604,19 @@
         <v>8</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:12">
@@ -1583,10 +1625,10 @@
         <v>107</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E11" s="3">
         <v>100</v>
@@ -1598,19 +1640,19 @@
         <v>8</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:12">
@@ -1619,10 +1661,10 @@
         <v>108</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12" s="3">
         <v>100</v>
@@ -1634,19 +1676,19 @@
         <v>8</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:12">
@@ -1655,34 +1697,34 @@
         <v>109</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E13" s="3">
         <v>100</v>
       </c>
       <c r="F13" s="3">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G13" s="3">
         <v>8</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:12">
@@ -1691,34 +1733,34 @@
         <v>110</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" s="3">
         <v>100</v>
       </c>
       <c r="F14" s="3">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="G14" s="3">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:12">
@@ -1730,7 +1772,7 @@
         <v>42</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E15" s="3">
         <v>300</v>
@@ -1742,19 +1784,19 @@
         <v>12</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:12">
@@ -1763,10 +1805,10 @@
         <v>202</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E16" s="3">
         <v>300</v>
@@ -1778,19 +1820,19 @@
         <v>12</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:12">
@@ -1799,10 +1841,10 @@
         <v>203</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E17" s="3">
         <v>300</v>
@@ -1814,19 +1856,19 @@
         <v>12</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:12">
@@ -1835,10 +1877,10 @@
         <v>204</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E18" s="3">
         <v>300</v>
@@ -1850,19 +1892,19 @@
         <v>12</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:12">
@@ -1871,10 +1913,10 @@
         <v>205</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E19" s="3">
         <v>300</v>
@@ -1886,19 +1928,19 @@
         <v>12</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:12">
@@ -1907,10 +1949,10 @@
         <v>206</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E20" s="3">
         <v>300</v>
@@ -1922,19 +1964,19 @@
         <v>12</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:12">
@@ -1943,10 +1985,10 @@
         <v>207</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E21" s="3">
         <v>300</v>
@@ -1958,19 +2000,19 @@
         <v>12</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:12">
@@ -1979,10 +2021,10 @@
         <v>208</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E22" s="3">
         <v>300</v>
@@ -1994,19 +2036,19 @@
         <v>12</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:12">
@@ -2015,10 +2057,10 @@
         <v>209</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E23" s="3">
         <v>300</v>
@@ -2030,19 +2072,19 @@
         <v>12</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:12">
@@ -2051,10 +2093,10 @@
         <v>210</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E24" s="3">
         <v>300</v>
@@ -2066,19 +2108,19 @@
         <v>12</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:12">
@@ -2087,10 +2129,10 @@
         <v>211</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E25" s="3">
         <v>300</v>
@@ -2102,19 +2144,19 @@
         <v>12</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:12">
@@ -2123,10 +2165,10 @@
         <v>212</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E26" s="3">
         <v>300</v>
@@ -2138,19 +2180,19 @@
         <v>12</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:12">
@@ -2159,10 +2201,10 @@
         <v>301</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E27" s="3">
         <v>500</v>
@@ -2174,19 +2216,19 @@
         <v>4</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:12">
@@ -2195,10 +2237,10 @@
         <v>302</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E28" s="3">
         <v>500</v>
@@ -2210,19 +2252,19 @@
         <v>4</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:12">
@@ -2231,10 +2273,10 @@
         <v>303</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E29" s="3">
         <v>500</v>
@@ -2246,19 +2288,19 @@
         <v>4</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:12">
@@ -2267,10 +2309,10 @@
         <v>304</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E30" s="3">
         <v>500</v>
@@ -2282,19 +2324,19 @@
         <v>4</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1" spans="1:12">
@@ -2303,10 +2345,10 @@
         <v>401</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E31" s="3">
         <v>500</v>
@@ -2318,19 +2360,19 @@
         <v>20</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
+      </c>
+      <c r="J31" s="3">
+        <v>201</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1" spans="1:12">
@@ -2339,10 +2381,10 @@
         <v>402</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E32" s="3">
         <v>300</v>
@@ -2354,19 +2396,19 @@
         <v>10</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1" spans="2:12">
@@ -2374,34 +2416,34 @@
         <v>501</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E33" s="3">
-        <v>100</v>
+        <v>4000</v>
       </c>
       <c r="F33" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G33" s="3">
         <v>-1</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>65</v>
+        <v>72</v>
+      </c>
+      <c r="J33" s="3">
+        <v>10</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="2:12">
@@ -2409,34 +2451,34 @@
         <v>502</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E34" s="3">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="F34" s="3">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="G34" s="3">
         <v>-1</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
+      </c>
+      <c r="J34" s="3">
+        <v>10</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="2:12">
@@ -2444,34 +2486,34 @@
         <v>503</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E35" s="3">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="F35" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G35" s="3">
         <v>-1</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>65</v>
+        <v>76</v>
+      </c>
+      <c r="J35" s="3">
+        <v>10</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1" spans="2:12">
@@ -2479,34 +2521,34 @@
         <v>504</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E36" s="3">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="F36" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G36" s="3">
         <v>-1</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>65</v>
+        <v>78</v>
+      </c>
+      <c r="J36" s="3">
+        <v>10</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2390,7 +2390,7 @@
         <v>300</v>
       </c>
       <c r="F32" s="3">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G32" s="3">
         <v>10</v>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="87">
   <si>
     <t>##var</t>
   </si>
@@ -43,6 +43,9 @@
     <t>SpecieType</t>
   </si>
   <si>
+    <t>BossType</t>
+  </si>
+  <si>
     <t>HP</t>
   </si>
   <si>
@@ -79,6 +82,9 @@
     <t>HuntingConfig.Enum.ESpecieType</t>
   </si>
   <si>
+    <t>HuntingConfig.Enum.EBossType</t>
+  </si>
+  <si>
     <t>float</t>
   </si>
   <si>
@@ -106,6 +112,9 @@
     <t>物种类型</t>
   </si>
   <si>
+    <t>Boss类型</t>
+  </si>
+  <si>
     <t>血量</t>
   </si>
   <si>
@@ -136,6 +145,9 @@
     <t>Small</t>
   </si>
   <si>
+    <t>None</t>
+  </si>
+  <si>
     <t>Meat:5|Bullet:0|ThreeKPCoin:0|Energy:5</t>
   </si>
   <si>
@@ -238,34 +250,46 @@
     <t>101,102,103,104</t>
   </si>
   <si>
+    <t>北极熊</t>
+  </si>
+  <si>
+    <t>Boss</t>
+  </si>
+  <si>
+    <t>BeiJiXiong</t>
+  </si>
+  <si>
+    <t>Meat:200|Bullet:0|ThreeKPCoin:0|Energy:0</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_boss_beijixiong</t>
+  </si>
+  <si>
+    <t>猛犸象</t>
+  </si>
+  <si>
+    <t>MengMaXiang</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_boss_mengmaxiang</t>
+  </si>
+  <si>
     <t>雪猩猩</t>
   </si>
   <si>
-    <t>Boss</t>
-  </si>
-  <si>
-    <t>Meat:200|Bullet:0|ThreeKPCoin:0|Energy:0</t>
+    <t>XueXingXing</t>
   </si>
   <si>
     <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_boss_xuexingxing</t>
   </si>
   <si>
-    <t>猛犸象</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_boss_mengmaxiang</t>
-  </si>
-  <si>
     <t>三角龙</t>
   </si>
   <si>
+    <t>SanJiaoLong</t>
+  </si>
+  <si>
     <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_boss_sanjiaolong</t>
-  </si>
-  <si>
-    <t>北极熊</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_boss_beijixiong</t>
   </si>
 </sst>
 </file>
@@ -1238,20 +1262,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="3" width="28.625" customWidth="1"/>
-    <col min="4" max="4" width="48.625" customWidth="1"/>
-    <col min="5" max="7" width="28.625" customWidth="1"/>
-    <col min="8" max="8" width="62.7833333333333" customWidth="1"/>
-    <col min="9" max="9" width="78.625" customWidth="1"/>
-    <col min="10" max="10" width="28.625" customWidth="1"/>
-    <col min="11" max="11" width="76.625" customWidth="1"/>
-    <col min="12" max="12" width="28.625" customWidth="1"/>
+    <col min="4" max="5" width="36.625" customWidth="1"/>
+    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="9" max="9" width="62.7833333333333" customWidth="1"/>
+    <col min="10" max="10" width="78.625" customWidth="1"/>
+    <col min="11" max="11" width="28.625" customWidth="1"/>
+    <col min="12" max="12" width="76.625" customWidth="1"/>
+    <col min="13" max="13" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:12">
+    <row r="1" ht="28" customHeight="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1288,1267 +1312,1375 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" ht="28" customHeight="1" spans="1:12">
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="K2" s="2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:12">
+        <v>15</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:12">
+        <v>22</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="I4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K4" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:12">
+        <v>34</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1" spans="1:13">
       <c r="A5" s="3"/>
       <c r="B5" s="3">
         <v>101</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="3">
+        <v>37</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="3">
         <v>100</v>
       </c>
-      <c r="F5" s="3">
+      <c r="G5" s="3">
         <v>2</v>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="3">
         <v>8</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:12">
+        <v>42</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:13">
       <c r="A6" s="3"/>
       <c r="B6" s="3">
         <v>102</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="3">
+        <v>37</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="3">
         <v>100</v>
       </c>
-      <c r="F6" s="3">
+      <c r="G6" s="3">
         <v>2</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="3">
         <v>8</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="I6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="L6" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:12">
+        <v>42</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:13">
       <c r="A7" s="3"/>
       <c r="B7" s="3">
         <v>103</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="3">
+        <v>100</v>
+      </c>
+      <c r="G7" s="3">
+        <v>2</v>
+      </c>
+      <c r="H7" s="3">
+        <v>8</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="3">
-        <v>100</v>
-      </c>
-      <c r="F7" s="3">
-        <v>2</v>
-      </c>
-      <c r="G7" s="3">
-        <v>8</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:12">
+      <c r="M7" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1" spans="1:13">
       <c r="A8" s="3"/>
       <c r="B8" s="3">
         <v>104</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="3">
+        <v>100</v>
+      </c>
+      <c r="G8" s="3">
+        <v>2</v>
+      </c>
+      <c r="H8" s="3">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="3">
-        <v>100</v>
-      </c>
-      <c r="F8" s="3">
-        <v>2</v>
-      </c>
-      <c r="G8" s="3">
-        <v>8</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:12">
+      <c r="M8" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1" spans="1:13">
       <c r="A9" s="3"/>
       <c r="B9" s="3">
         <v>105</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="3">
+        <v>100</v>
+      </c>
+      <c r="G9" s="3">
+        <v>2</v>
+      </c>
+      <c r="H9" s="3">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="3">
-        <v>100</v>
-      </c>
-      <c r="F9" s="3">
-        <v>2</v>
-      </c>
-      <c r="G9" s="3">
-        <v>8</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:12">
+      <c r="M9" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:13">
       <c r="A10" s="3"/>
       <c r="B10" s="3">
         <v>106</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="3">
+        <v>100</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2</v>
+      </c>
+      <c r="H10" s="3">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="3">
-        <v>100</v>
-      </c>
-      <c r="F10" s="3">
-        <v>2</v>
-      </c>
-      <c r="G10" s="3">
-        <v>8</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:12">
+      <c r="M10" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:13">
       <c r="A11" s="3"/>
       <c r="B11" s="3">
         <v>107</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="3">
+        <v>100</v>
+      </c>
+      <c r="G11" s="3">
+        <v>2</v>
+      </c>
+      <c r="H11" s="3">
+        <v>8</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="3">
-        <v>100</v>
-      </c>
-      <c r="F11" s="3">
-        <v>2</v>
-      </c>
-      <c r="G11" s="3">
-        <v>8</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:12">
+      <c r="M11" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:13">
       <c r="A12" s="3"/>
       <c r="B12" s="3">
         <v>108</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="3">
+        <v>100</v>
+      </c>
+      <c r="G12" s="3">
+        <v>2</v>
+      </c>
+      <c r="H12" s="3">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="3">
-        <v>100</v>
-      </c>
-      <c r="F12" s="3">
-        <v>2</v>
-      </c>
-      <c r="G12" s="3">
-        <v>8</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:12">
+      <c r="M12" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:13">
       <c r="A13" s="3"/>
       <c r="B13" s="3">
         <v>109</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="3">
+        <v>37</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="3">
         <v>100</v>
       </c>
-      <c r="F13" s="3">
+      <c r="G13" s="3">
         <v>3.5</v>
       </c>
-      <c r="G13" s="3">
+      <c r="H13" s="3">
         <v>8</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="I13" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="1:12">
+        <v>43</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1" spans="1:13">
       <c r="A14" s="3"/>
       <c r="B14" s="3">
         <v>110</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="3">
+        <v>37</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>0.6</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>16</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="I14" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:12">
+        <v>43</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1" spans="1:13">
       <c r="A15" s="3"/>
       <c r="B15" s="3">
         <v>201</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="3">
+        <v>300</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H15" s="3">
+        <v>12</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="3">
-        <v>300</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="G15" s="3">
-        <v>12</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1" spans="1:12">
+      <c r="M15" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:13">
       <c r="A16" s="3"/>
       <c r="B16" s="3">
         <v>202</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="3">
+        <v>52</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="3">
         <v>300</v>
       </c>
-      <c r="F16" s="3">
+      <c r="G16" s="3">
         <v>2.5</v>
       </c>
-      <c r="G16" s="3">
+      <c r="H16" s="3">
         <v>12</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="I16" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1" spans="1:12">
+        <v>42</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="1:13">
       <c r="A17" s="3"/>
       <c r="B17" s="3">
         <v>203</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="3">
+        <v>300</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H17" s="3">
+        <v>12</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="3">
-        <v>300</v>
-      </c>
-      <c r="F17" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="G17" s="3">
-        <v>12</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1" spans="1:12">
+        <v>42</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1" spans="1:13">
       <c r="A18" s="3"/>
       <c r="B18" s="3">
         <v>204</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="3">
+        <v>300</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H18" s="3">
+        <v>12</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="3">
-        <v>300</v>
-      </c>
-      <c r="F18" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="G18" s="3">
-        <v>12</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="K18" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:12">
+        <v>42</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1" spans="1:13">
       <c r="A19" s="3"/>
       <c r="B19" s="3">
         <v>205</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="3">
+        <v>52</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" s="3">
         <v>300</v>
       </c>
-      <c r="F19" s="3">
+      <c r="G19" s="3">
         <v>2.5</v>
       </c>
-      <c r="G19" s="3">
+      <c r="H19" s="3">
         <v>12</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="I19" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="1:12">
+        <v>42</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1" spans="1:13">
       <c r="A20" s="3"/>
       <c r="B20" s="3">
         <v>206</v>
       </c>
       <c r="C20" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="3">
+        <v>300</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H20" s="3">
+        <v>12</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="3">
-        <v>300</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="G20" s="3">
-        <v>12</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="K20" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1" spans="1:12">
+        <v>42</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1" spans="1:13">
       <c r="A21" s="3"/>
       <c r="B21" s="3">
         <v>207</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" s="3">
+        <v>300</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H21" s="3">
+        <v>12</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" s="3">
-        <v>300</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="G21" s="3">
-        <v>12</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="K21" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1" spans="1:12">
+        <v>42</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1" spans="1:13">
       <c r="A22" s="3"/>
       <c r="B22" s="3">
         <v>208</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E22" s="3">
+        <v>52</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2.5</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="I22" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1" spans="1:12">
+        <v>42</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:13">
       <c r="A23" s="3"/>
       <c r="B23" s="3">
         <v>209</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="3">
+        <v>300</v>
+      </c>
+      <c r="G23" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H23" s="3">
+        <v>12</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E23" s="3">
-        <v>300</v>
-      </c>
-      <c r="F23" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="G23" s="3">
-        <v>12</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="K23" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1" spans="1:12">
+        <v>42</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1" spans="1:13">
       <c r="A24" s="3"/>
       <c r="B24" s="3">
         <v>210</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="3">
+        <v>300</v>
+      </c>
+      <c r="G24" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H24" s="3">
+        <v>12</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E24" s="3">
-        <v>300</v>
-      </c>
-      <c r="F24" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="G24" s="3">
-        <v>12</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="K24" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1" spans="1:12">
+        <v>42</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1" spans="1:13">
       <c r="A25" s="3"/>
       <c r="B25" s="3">
         <v>211</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E25" s="3">
+        <v>52</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" s="3">
         <v>300</v>
       </c>
-      <c r="F25" s="3">
+      <c r="G25" s="3">
         <v>2.5</v>
       </c>
-      <c r="G25" s="3">
+      <c r="H25" s="3">
         <v>12</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="I25" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1" spans="1:12">
+        <v>42</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1" spans="1:13">
       <c r="A26" s="3"/>
       <c r="B26" s="3">
         <v>212</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" s="3">
+        <v>300</v>
+      </c>
+      <c r="G26" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H26" s="3">
+        <v>12</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E26" s="3">
-        <v>300</v>
-      </c>
-      <c r="F26" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="G26" s="3">
-        <v>12</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="K26" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1" spans="1:12">
+        <v>42</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1" spans="1:13">
       <c r="A27" s="3"/>
       <c r="B27" s="3">
         <v>301</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E27" s="3">
+        <v>61</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F27" s="3">
         <v>500</v>
-      </c>
-      <c r="F27" s="3">
-        <v>4</v>
       </c>
       <c r="G27" s="3">
         <v>4</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>58</v>
+      <c r="H27" s="3">
+        <v>4</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1" spans="1:12">
+        <v>42</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1" spans="1:13">
       <c r="A28" s="3"/>
       <c r="B28" s="3">
         <v>302</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E28" s="3">
+        <v>61</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="3">
         <v>500</v>
-      </c>
-      <c r="F28" s="3">
-        <v>4</v>
       </c>
       <c r="G28" s="3">
         <v>4</v>
       </c>
-      <c r="H28" s="3" t="s">
-        <v>55</v>
+      <c r="H28" s="3">
+        <v>4</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1" spans="1:12">
+        <v>42</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1" spans="1:13">
       <c r="A29" s="3"/>
       <c r="B29" s="3">
         <v>303</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E29" s="3">
+        <v>61</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F29" s="3">
         <v>500</v>
-      </c>
-      <c r="F29" s="3">
-        <v>4</v>
       </c>
       <c r="G29" s="3">
         <v>4</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>58</v>
+      <c r="H29" s="3">
+        <v>4</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1" spans="1:12">
+        <v>42</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1" spans="1:13">
       <c r="A30" s="3"/>
       <c r="B30" s="3">
         <v>304</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E30" s="3">
+        <v>61</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F30" s="3">
         <v>500</v>
-      </c>
-      <c r="F30" s="3">
-        <v>4</v>
       </c>
       <c r="G30" s="3">
         <v>4</v>
       </c>
-      <c r="H30" s="3" t="s">
-        <v>55</v>
+      <c r="H30" s="3">
+        <v>4</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1" spans="1:12">
+        <v>42</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1" spans="1:13">
       <c r="A31" s="3"/>
       <c r="B31" s="3">
         <v>401</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E31" s="3">
+        <v>65</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F31" s="3">
         <v>500</v>
       </c>
-      <c r="F31" s="3">
+      <c r="G31" s="3">
         <v>1.5</v>
       </c>
-      <c r="G31" s="3">
+      <c r="H31" s="3">
         <v>20</v>
       </c>
-      <c r="H31" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="I31" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="J31" s="3">
+        <v>66</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K31" s="3">
         <v>201</v>
       </c>
-      <c r="K31" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="L31" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1" spans="1:12">
+        <v>43</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1" spans="1:13">
       <c r="A32" s="3"/>
       <c r="B32" s="3">
         <v>402</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E32" s="3">
+        <v>69</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>10</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="I32" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>39</v>
+        <v>70</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1" spans="2:12">
+        <v>43</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1" spans="2:13">
       <c r="B33" s="3">
         <v>501</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E33" s="3">
+        <v>74</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F33" s="3">
         <v>4000</v>
       </c>
-      <c r="F33" s="3">
-        <v>1</v>
-      </c>
       <c r="G33" s="3">
+        <v>3</v>
+      </c>
+      <c r="H33" s="3">
         <v>-1</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="I33" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="J33" s="3">
+        <v>76</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K33" s="3">
         <v>10</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="L33" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1" spans="2:12">
+        <v>43</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1" spans="2:13">
       <c r="B34" s="3">
         <v>502</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E34" s="3">
+        <v>74</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F34" s="3">
         <v>4000</v>
       </c>
-      <c r="F34" s="3">
+      <c r="G34" s="3">
         <v>1.4</v>
       </c>
-      <c r="G34" s="3">
+      <c r="H34" s="3">
         <v>-1</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="I34" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J34" s="3">
+        <v>76</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K34" s="3">
         <v>10</v>
       </c>
-      <c r="K34" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="L34" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1" spans="2:12">
+        <v>43</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1" spans="2:13">
       <c r="B35" s="3">
         <v>503</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E35" s="3">
+        <v>74</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F35" s="3">
         <v>4000</v>
       </c>
-      <c r="F35" s="3">
-        <v>3</v>
-      </c>
       <c r="G35" s="3">
+        <v>1</v>
+      </c>
+      <c r="H35" s="3">
         <v>-1</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K35" s="3">
         <v>10</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="L35" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1" spans="2:12">
+        <v>43</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1" spans="2:13">
       <c r="B36" s="3">
         <v>504</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E36" s="3">
+        <v>74</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F36" s="3">
         <v>4000</v>
       </c>
-      <c r="F36" s="3">
+      <c r="G36" s="3">
         <v>3</v>
       </c>
-      <c r="G36" s="3">
+      <c r="H36" s="3">
         <v>-1</v>
       </c>
-      <c r="H36" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="I36" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="J36" s="3">
+        <v>76</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="K36" s="3">
         <v>10</v>
       </c>
-      <c r="K36" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="L36" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="65">
   <si>
     <t>##var</t>
   </si>
@@ -52,21 +52,12 @@
     <t>MoveSpeed</t>
   </si>
   <si>
-    <t>StayTime</t>
-  </si>
-  <si>
     <t>DropRewards</t>
   </si>
   <si>
-    <t>PrefabResourcePath</t>
-  </si>
-  <si>
     <t>DropMeatEffectID</t>
   </si>
   <si>
-    <t>IconResourcePath</t>
-  </si>
-  <si>
     <t>Comment</t>
   </si>
   <si>
@@ -121,70 +112,46 @@
     <t>移动速度</t>
   </si>
   <si>
-    <t>驻场时间</t>
-  </si>
-  <si>
     <t>掉落奖励</t>
   </si>
   <si>
-    <t>预制体资源路径</t>
-  </si>
-  <si>
     <t>掉落肉特效ID</t>
   </si>
   <si>
-    <t>图标资源路径</t>
-  </si>
-  <si>
     <t>备注</t>
   </si>
   <si>
+    <t>兔子</t>
+  </si>
+  <si>
+    <t>Small</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Meat:5|Bullet:0|ThreeKPCoin:0|Energy:5</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
     <t>野鸡</t>
   </si>
   <si>
-    <t>Small</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>Meat:5|Bullet:0|ThreeKPCoin:0|Energy:5</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_small_yeji</t>
-  </si>
-  <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>Assets/Arts/UI/Sprites/Gameplay/Animals/Skull_01</t>
-  </si>
-  <si>
-    <t>/</t>
-  </si>
-  <si>
-    <t>兔子</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_small_tuzi</t>
-  </si>
-  <si>
-    <t>小体型怪</t>
+    <t>企鹅</t>
+  </si>
+  <si>
+    <t>9,16</t>
   </si>
   <si>
     <t>白狐</t>
   </si>
   <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_small_baihu</t>
-  </si>
-  <si>
-    <t>9,16</t>
-  </si>
-  <si>
-    <t>企鹅</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_small_qie</t>
+    <t>野猪</t>
   </si>
   <si>
     <t>Medium</t>
@@ -193,24 +160,9 @@
     <t>Meat:10|Bullet:0|ThreeKPCoin:0|Energy:10</t>
   </si>
   <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_medium_yezhu</t>
-  </si>
-  <si>
     <t>鹿</t>
   </si>
   <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_forest_medium_lu</t>
-  </si>
-  <si>
-    <t>野猪</t>
-  </si>
-  <si>
-    <t>中体型怪</t>
-  </si>
-  <si>
-    <t>Meat:10|Bullet:0|ThreeKPCoin:0|Energy:20</t>
-  </si>
-  <si>
     <t>豹子</t>
   </si>
   <si>
@@ -220,7 +172,7 @@
     <t>Meat:20|Bullet:0|ThreeKPCoin:0|Energy:20</t>
   </si>
   <si>
-    <t>大体型怪</t>
+    <t>老虎</t>
   </si>
   <si>
     <t>弹药怪</t>
@@ -232,9 +184,6 @@
     <t>Meat:0|Bullet:1|ThreeKPCoin:0|Energy:20</t>
   </si>
   <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_special_bulletcoin</t>
-  </si>
-  <si>
     <t>金币怪</t>
   </si>
   <si>
@@ -244,9 +193,6 @@
     <t>Meat:0|Bullet:0|ThreeKPCoin:10|Energy:20</t>
   </si>
   <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_special_threekpcoin</t>
-  </si>
-  <si>
     <t>101,102,103,104</t>
   </si>
   <si>
@@ -262,34 +208,22 @@
     <t>Meat:200|Bullet:0|ThreeKPCoin:0|Energy:0</t>
   </si>
   <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_boss_beijixiong</t>
-  </si>
-  <si>
     <t>猛犸象</t>
   </si>
   <si>
     <t>MengMaXiang</t>
   </si>
   <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_boss_mengmaxiang</t>
-  </si>
-  <si>
     <t>雪猩猩</t>
   </si>
   <si>
     <t>XueXingXing</t>
   </si>
   <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_boss_xuexingxing</t>
-  </si>
-  <si>
     <t>三角龙</t>
   </si>
   <si>
     <t>SanJiaoLong</t>
-  </si>
-  <si>
-    <t>Assets/Arts/Prefabs/Animals/pf_animal_snow_boss_sanjiaolong</t>
   </si>
 </sst>
 </file>
@@ -1262,20 +1196,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="3" width="28.625" customWidth="1"/>
     <col min="4" max="5" width="36.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
-    <col min="9" max="9" width="62.7833333333333" customWidth="1"/>
-    <col min="10" max="10" width="78.625" customWidth="1"/>
-    <col min="11" max="11" width="28.625" customWidth="1"/>
-    <col min="12" max="12" width="76.625" customWidth="1"/>
-    <col min="13" max="13" width="28.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="62.7833333333333" customWidth="1"/>
+    <col min="9" max="10" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:13">
+    <row r="1" ht="28" customHeight="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1306,152 +1237,116 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:10">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="1" t="s">
+    <row r="3" ht="28" customHeight="1" spans="1:10">
+      <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="2" t="s">
+      <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:10">
+      <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>15</v>
+      <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:13">
+    <row r="5" ht="28" customHeight="1" spans="1:10">
       <c r="A5" s="3"/>
       <c r="B5" s="3">
         <v>101</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
@@ -1459,38 +1354,29 @@
       <c r="G5" s="3">
         <v>2</v>
       </c>
-      <c r="H5" s="3">
-        <v>8</v>
+      <c r="H5" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="1:13">
+    <row r="6" ht="28" customHeight="1" spans="1:10">
       <c r="A6" s="3"/>
       <c r="B6" s="3">
         <v>102</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
@@ -1498,1189 +1384,370 @@
       <c r="G6" s="3">
         <v>2</v>
       </c>
-      <c r="H6" s="3">
-        <v>8</v>
+      <c r="H6" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1" spans="1:13">
+    <row r="7" ht="28" customHeight="1" spans="1:10">
       <c r="A7" s="3"/>
       <c r="B7" s="3">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F7" s="3">
         <v>100</v>
       </c>
       <c r="G7" s="3">
-        <v>2</v>
-      </c>
-      <c r="H7" s="3">
-        <v>8</v>
+        <v>3.5</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1" spans="1:13">
+    <row r="8" ht="28" customHeight="1" spans="1:10">
       <c r="A8" s="3"/>
       <c r="B8" s="3">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F8" s="3">
         <v>100</v>
       </c>
       <c r="G8" s="3">
-        <v>2</v>
-      </c>
-      <c r="H8" s="3">
-        <v>8</v>
+        <v>0.6</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1" spans="1:13">
+    <row r="9" ht="28" customHeight="1" spans="1:10">
       <c r="A9" s="3"/>
       <c r="B9" s="3">
-        <v>105</v>
+        <v>201</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F9" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G9" s="3">
-        <v>2</v>
-      </c>
-      <c r="H9" s="3">
-        <v>8</v>
+        <v>1.5</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1" spans="1:13">
+    <row r="10" ht="28" customHeight="1" spans="1:10">
       <c r="A10" s="3"/>
       <c r="B10" s="3">
-        <v>106</v>
+        <v>202</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F10" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G10" s="3">
-        <v>2</v>
-      </c>
-      <c r="H10" s="3">
-        <v>8</v>
+        <v>2.5</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1" spans="1:13">
+    <row r="11" ht="28" customHeight="1" spans="1:10">
       <c r="A11" s="3"/>
       <c r="B11" s="3">
-        <v>107</v>
+        <v>301</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="3">
+        <v>500</v>
+      </c>
+      <c r="G11" s="3">
+        <v>4</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="3">
-        <v>100</v>
-      </c>
-      <c r="G11" s="3">
-        <v>2</v>
-      </c>
-      <c r="H11" s="3">
-        <v>8</v>
-      </c>
       <c r="I11" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1" spans="1:13">
+    <row r="12" ht="28" customHeight="1" spans="1:10">
       <c r="A12" s="3"/>
       <c r="B12" s="3">
-        <v>108</v>
+        <v>302</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F12" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G12" s="3">
         <v>2</v>
       </c>
-      <c r="H12" s="3">
-        <v>8</v>
+      <c r="H12" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1" spans="1:13">
+    <row r="13" ht="28" customHeight="1" spans="1:10">
       <c r="A13" s="3"/>
       <c r="B13" s="3">
-        <v>109</v>
+        <v>401</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F13" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G13" s="3">
-        <v>3.5</v>
-      </c>
-      <c r="H13" s="3">
-        <v>8</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>39</v>
+        <v>1.5</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I13" s="3">
+        <v>201</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1" spans="1:13">
+    <row r="14" ht="28" customHeight="1" spans="1:10">
       <c r="A14" s="3"/>
       <c r="B14" s="3">
-        <v>110</v>
+        <v>402</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>37</v>
+        <v>51</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F14" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G14" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="H14" s="3">
-        <v>16</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>39</v>
+        <v>1</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1" spans="1:13">
-      <c r="A15" s="3"/>
+    <row r="15" ht="28" customHeight="1" spans="2:10">
       <c r="B15" s="3">
-        <v>201</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>52</v>
+        <v>501</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F15" s="3">
-        <v>300</v>
+        <v>4000</v>
       </c>
       <c r="G15" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="H15" s="3">
-        <v>12</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>53</v>
+        <v>3</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I15" s="3">
+        <v>10</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1" spans="1:13">
-      <c r="A16" s="3"/>
+    <row r="16" ht="28" customHeight="1" spans="2:10">
       <c r="B16" s="3">
-        <v>202</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>52</v>
+        <v>502</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F16" s="3">
-        <v>300</v>
+        <v>4000</v>
       </c>
       <c r="G16" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="H16" s="3">
-        <v>12</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>53</v>
+        <v>1.4</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I16" s="3">
+        <v>10</v>
       </c>
       <c r="J16" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="2:10">
+      <c r="B17" s="3">
+        <v>503</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>43</v>
+      <c r="E17" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I17" s="3">
+        <v>10</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1" spans="1:13">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3">
-        <v>203</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" s="3">
-        <v>300</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="H17" s="3">
-        <v>12</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1" spans="1:13">
-      <c r="A18" s="3"/>
+    <row r="18" ht="28" customHeight="1" spans="2:10">
       <c r="B18" s="3">
-        <v>204</v>
-      </c>
-      <c r="C18" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" s="3">
+        <v>4000</v>
+      </c>
+      <c r="G18" s="3">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="3">
-        <v>300</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="H18" s="3">
-        <v>12</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>53</v>
+      <c r="I18" s="3">
+        <v>10</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:13">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3">
-        <v>205</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19" s="3">
-        <v>300</v>
-      </c>
-      <c r="G19" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="H19" s="3">
-        <v>12</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="1:13">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3">
-        <v>206</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="3">
-        <v>300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="H20" s="3">
-        <v>12</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1" spans="1:13">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3">
-        <v>207</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="3">
-        <v>300</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="H21" s="3">
-        <v>12</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1" spans="1:13">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3">
-        <v>208</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="3">
-        <v>300</v>
-      </c>
-      <c r="G22" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="H22" s="3">
-        <v>12</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1" spans="1:13">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3">
-        <v>209</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="3">
-        <v>300</v>
-      </c>
-      <c r="G23" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="H23" s="3">
-        <v>12</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1" spans="1:13">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3">
-        <v>210</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="3">
-        <v>300</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="H24" s="3">
-        <v>12</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1" spans="1:13">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3">
-        <v>211</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="3">
-        <v>300</v>
-      </c>
-      <c r="G25" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="H25" s="3">
-        <v>12</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1" spans="1:13">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3">
-        <v>212</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F26" s="3">
-        <v>300</v>
-      </c>
-      <c r="G26" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="H26" s="3">
-        <v>12</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1" spans="1:13">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3">
-        <v>301</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" s="3">
-        <v>500</v>
-      </c>
-      <c r="G27" s="3">
-        <v>4</v>
-      </c>
-      <c r="H27" s="3">
-        <v>4</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1" spans="1:13">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3">
-        <v>302</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" s="3">
-        <v>500</v>
-      </c>
-      <c r="G28" s="3">
-        <v>4</v>
-      </c>
-      <c r="H28" s="3">
-        <v>4</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1" spans="1:13">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3">
-        <v>303</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" s="3">
-        <v>500</v>
-      </c>
-      <c r="G29" s="3">
-        <v>4</v>
-      </c>
-      <c r="H29" s="3">
-        <v>4</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1" spans="1:13">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3">
-        <v>304</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F30" s="3">
-        <v>500</v>
-      </c>
-      <c r="G30" s="3">
-        <v>4</v>
-      </c>
-      <c r="H30" s="3">
-        <v>4</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1" spans="1:13">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3">
-        <v>401</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F31" s="3">
-        <v>500</v>
-      </c>
-      <c r="G31" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="H31" s="3">
-        <v>20</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="K31" s="3">
-        <v>201</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1" spans="1:13">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3">
-        <v>402</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F32" s="3">
-        <v>300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>1</v>
-      </c>
-      <c r="H32" s="3">
-        <v>10</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1" spans="2:13">
-      <c r="B33" s="3">
-        <v>501</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F33" s="3">
-        <v>4000</v>
-      </c>
-      <c r="G33" s="3">
-        <v>3</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-1</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="K33" s="3">
-        <v>10</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1" spans="2:13">
-      <c r="B34" s="3">
-        <v>502</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F34" s="3">
-        <v>4000</v>
-      </c>
-      <c r="G34" s="3">
-        <v>1.4</v>
-      </c>
-      <c r="H34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="K34" s="3">
-        <v>10</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1" spans="2:13">
-      <c r="B35" s="3">
-        <v>503</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F35" s="3">
-        <v>4000</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-1</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="K35" s="3">
-        <v>10</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1" spans="2:13">
-      <c r="B36" s="3">
-        <v>504</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F36" s="3">
-        <v>4000</v>
-      </c>
-      <c r="G36" s="3">
-        <v>3</v>
-      </c>
-      <c r="H36" s="3">
-        <v>-1</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="K36" s="3">
-        <v>10</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -112,7 +112,7 @@
     <t>移动速度</t>
   </si>
   <si>
-    <t>掉落奖励</t>
+    <t>掉落奖励（从左往右：肉/子弹/三千盘金币/能量</t>
   </si>
   <si>
     <t>掉落肉特效ID</t>
@@ -175,7 +175,7 @@
     <t>老虎</t>
   </si>
   <si>
-    <t>弹药怪</t>
+    <t>彩色大鹅</t>
   </si>
   <si>
     <t>Bullet</t>
@@ -184,13 +184,13 @@
     <t>Meat:0|Bullet:1|ThreeKPCoin:0|Energy:20</t>
   </si>
   <si>
-    <t>金币怪</t>
+    <t>金币人</t>
   </si>
   <si>
     <t>ThreeKPCoin</t>
   </si>
   <si>
-    <t>Meat:0|Bullet:0|ThreeKPCoin:10|Energy:20</t>
+    <t>Meat:0|Bullet:0|ThreeKPCoin:1|Energy:0</t>
   </si>
   <si>
     <t>101,102,103,104</t>
@@ -208,7 +208,7 @@
     <t>Meat:200|Bullet:0|ThreeKPCoin:0|Energy:0</t>
   </si>
   <si>
-    <t>猛犸象</t>
+    <t>邪恶猛犸骑士</t>
   </si>
   <si>
     <t>MengMaXiang</t>
@@ -220,7 +220,7 @@
     <t>XueXingXing</t>
   </si>
   <si>
-    <t>三角龙</t>
+    <t>阳光三角龙</t>
   </si>
   <si>
     <t>SanJiaoLong</t>
@@ -401,7 +401,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -410,6 +410,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -595,7 +601,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -607,6 +613,32 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -742,7 +774,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -754,119 +786,119 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -876,10 +908,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1321,13 +1365,13 @@
       <c r="F4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J4" s="2" t="s">
@@ -1335,418 +1379,418 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:10">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6">
         <v>101</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="6">
         <v>100</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="6">
         <v>2</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:10">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6">
         <v>102</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="6">
         <v>100</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="6">
         <v>2</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:10">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6">
         <v>109</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="6">
         <v>100</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="6">
         <v>3.5</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:10">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6">
         <v>110</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="6">
         <v>100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="6">
         <v>0.6</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:10">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6">
         <v>201</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="6">
         <v>300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="6">
         <v>1.5</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:10">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6">
         <v>202</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="6">
         <v>300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="6">
         <v>2.5</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:10">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6">
         <v>301</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="6">
         <v>500</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="6">
         <v>4</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:10">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6">
         <v>302</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="6">
         <v>500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="6">
         <v>2</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="J12" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:10">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6">
         <v>401</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="6">
         <v>500</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="6">
         <v>1.5</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="6">
         <v>201</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="J13" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:10">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6">
         <v>402</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="6">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="6">
         <v>1</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1" spans="2:10">
-      <c r="B15" s="3">
+    <row r="15" ht="28" customHeight="1" spans="1:10">
+      <c r="B15" s="6">
         <v>501</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="6">
         <v>4000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="6">
         <v>3</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="6">
         <v>10</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="J15" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1" spans="2:10">
-      <c r="B16" s="3">
+    <row r="16" ht="28" customHeight="1" spans="1:10">
+      <c r="B16" s="6">
         <v>502</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="6">
         <v>4000</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="6">
         <v>1.4</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="6">
         <v>10</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="J16" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="2:10">
-      <c r="B17" s="3">
+      <c r="B17" s="6">
         <v>503</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="6">
         <v>4000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="6">
         <v>1</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="H17" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="6">
         <v>10</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="J17" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="2:10">
-      <c r="B18" s="3">
+      <c r="B18" s="6">
         <v>504</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="6">
         <v>4000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="6">
         <v>3</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H18" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="6">
         <v>10</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="J18" s="6" t="s">
         <v>35</v>
       </c>
     </row>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -914,9 +914,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -924,6 +921,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1371,7 +1371,7 @@
       <c r="H4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="8" t="s">
         <v>28</v>
       </c>
       <c r="J4" s="2" t="s">
@@ -1379,418 +1379,418 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:10">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5">
         <v>101</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <v>100</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <v>2</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:10">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5">
         <v>102</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <v>100</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>2</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:10">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5">
         <v>109</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <v>100</v>
       </c>
-      <c r="G7" s="6">
-        <v>3.5</v>
-      </c>
-      <c r="H7" s="8" t="s">
+      <c r="G7" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:10">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5">
         <v>110</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <v>100</v>
       </c>
-      <c r="G8" s="6">
-        <v>0.6</v>
-      </c>
-      <c r="H8" s="8" t="s">
+      <c r="G8" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="H8" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:10">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5">
         <v>201</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <v>300</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>1.5</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:10">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5">
         <v>202</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <v>300</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="5">
         <v>2.5</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:10">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5">
         <v>301</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="5">
         <v>500</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="5">
         <v>4</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:10">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5">
         <v>302</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
         <v>500</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <v>2</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:10">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5">
         <v>401</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="5">
         <v>500</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="5">
         <v>1.5</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="5">
         <v>201</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:10">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5">
         <v>402</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="5">
         <v>300</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="5">
         <v>1</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="7" t="s">
         <v>53</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="J14" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1" spans="1:10">
-      <c r="B15" s="6">
+    <row r="15" ht="28" customHeight="1" spans="2:10">
+      <c r="B15" s="5">
         <v>501</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="5">
         <v>4000</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="5">
         <v>3</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="5">
         <v>10</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J15" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1" spans="1:10">
-      <c r="B16" s="6">
+    <row r="16" ht="28" customHeight="1" spans="2:10">
+      <c r="B16" s="5">
         <v>502</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="5">
         <v>4000</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="5">
         <v>1.4</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="5">
         <v>10</v>
       </c>
-      <c r="J16" s="6" t="s">
+      <c r="J16" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="2:10">
-      <c r="B17" s="6">
+      <c r="B17" s="5">
         <v>503</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="5">
         <v>4000</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="5">
         <v>1</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="5">
         <v>10</v>
       </c>
-      <c r="J17" s="6" t="s">
+      <c r="J17" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="2:10">
-      <c r="B18" s="6">
+      <c r="B18" s="5">
         <v>504</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="5">
         <v>4000</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="5">
         <v>3</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="5">
         <v>10</v>
       </c>
-      <c r="J18" s="6" t="s">
+      <c r="J18" s="5" t="s">
         <v>35</v>
       </c>
     </row>

--- a/Datas/Specie.xlsx
+++ b/Datas/Specie.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="62">
   <si>
     <t>##var</t>
   </si>
@@ -58,9 +58,6 @@
     <t>DropMeatEffectID</t>
   </si>
   <si>
-    <t>Comment</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -118,9 +115,6 @@
     <t>掉落肉特效ID</t>
   </si>
   <si>
-    <t>备注</t>
-  </si>
-  <si>
     <t>兔子</t>
   </si>
   <si>
@@ -134,9 +128,6 @@
   </si>
   <si>
     <t>1,2</t>
-  </si>
-  <si>
-    <t>/</t>
   </si>
   <si>
     <t>野鸡</t>
@@ -1240,17 +1231,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="3" width="28.625" customWidth="1"/>
     <col min="4" max="5" width="36.625" customWidth="1"/>
     <col min="6" max="7" width="28.625" customWidth="1"/>
     <col min="8" max="8" width="62.7833333333333" customWidth="1"/>
-    <col min="9" max="10" width="28.625" customWidth="1"/>
+    <col min="9" max="9" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:10">
+    <row r="1" ht="28" customHeight="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1278,119 +1269,107 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:9">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
+    <row r="3" ht="28" customHeight="1" spans="1:9">
+      <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>12</v>
+      <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="4" ht="28" customHeight="1" spans="1:9">
+      <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>19</v>
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:10">
+    <row r="5" ht="28" customHeight="1" spans="1:9">
       <c r="A5" s="5"/>
       <c r="B5" s="5">
         <v>101</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>32</v>
       </c>
       <c r="F5" s="5">
         <v>100</v>
@@ -1399,28 +1378,25 @@
         <v>2</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="1:10">
+    <row r="6" ht="28" customHeight="1" spans="1:9">
       <c r="A6" s="5"/>
       <c r="B6" s="5">
         <v>102</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F6" s="5">
         <v>100</v>
@@ -1429,28 +1405,25 @@
         <v>2</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1" spans="1:10">
+    <row r="7" ht="28" customHeight="1" spans="1:9">
       <c r="A7" s="5"/>
       <c r="B7" s="5">
         <v>109</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F7" s="5">
         <v>100</v>
@@ -1459,28 +1432,25 @@
         <v>0.6</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1" spans="1:10">
+    <row r="8" ht="28" customHeight="1" spans="1:9">
       <c r="A8" s="5"/>
       <c r="B8" s="5">
         <v>110</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F8" s="5">
         <v>100</v>
@@ -1489,28 +1459,25 @@
         <v>3.5</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J8" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1" spans="1:10">
+    <row r="9" ht="28" customHeight="1" spans="1:9">
       <c r="A9" s="5"/>
       <c r="B9" s="5">
         <v>201</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F9" s="5">
         <v>300</v>
@@ -1519,28 +1486,25 @@
         <v>1.5</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1" spans="1:10">
+    <row r="10" ht="28" customHeight="1" spans="1:9">
       <c r="A10" s="5"/>
       <c r="B10" s="5">
         <v>202</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F10" s="5">
         <v>300</v>
@@ -1549,88 +1513,79 @@
         <v>2.5</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1" spans="1:10">
+    <row r="11" ht="28" customHeight="1" spans="1:9">
       <c r="A11" s="5"/>
       <c r="B11" s="5">
         <v>301</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F11" s="5">
         <v>500</v>
       </c>
       <c r="G11" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1" spans="1:10">
+    <row r="12" ht="28" customHeight="1" spans="1:9">
       <c r="A12" s="5"/>
       <c r="B12" s="5">
         <v>302</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F12" s="5">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="G12" s="5">
         <v>2</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1" spans="1:10">
+    <row r="13" ht="28" customHeight="1" spans="1:9">
       <c r="A13" s="5"/>
       <c r="B13" s="5">
         <v>401</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F13" s="5">
         <v>500</v>
@@ -1639,28 +1594,25 @@
         <v>1.5</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I13" s="5">
         <v>201</v>
       </c>
-      <c r="J13" s="5" t="s">
-        <v>35</v>
-      </c>
     </row>
-    <row r="14" ht="28" customHeight="1" spans="1:10">
+    <row r="14" ht="28" customHeight="1" spans="1:9">
       <c r="A14" s="5"/>
       <c r="B14" s="5">
         <v>402</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F14" s="5">
         <v>300</v>
@@ -1669,129 +1621,114 @@
         <v>1</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1" spans="2:10">
+    <row r="15" ht="28" customHeight="1" spans="2:9">
       <c r="B15" s="5">
         <v>501</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F15" s="5">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="G15" s="5">
         <v>3</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I15" s="5">
         <v>10</v>
       </c>
-      <c r="J15" s="5" t="s">
-        <v>35</v>
-      </c>
     </row>
-    <row r="16" ht="28" customHeight="1" spans="2:10">
+    <row r="16" ht="28" customHeight="1" spans="2:9">
       <c r="B16" s="5">
         <v>502</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F16" s="5">
-        <v>4000</v>
+        <v>6001</v>
       </c>
       <c r="G16" s="5">
         <v>1.4</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I16" s="5">
         <v>10</v>
       </c>
-      <c r="J16" s="5" t="s">
-        <v>35</v>
-      </c>
     </row>
-    <row r="17" ht="28" customHeight="1" spans="2:10">
+    <row r="17" ht="28" customHeight="1" spans="2:9">
       <c r="B17" s="5">
         <v>503</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F17" s="5">
-        <v>4000</v>
+        <v>6002</v>
       </c>
       <c r="G17" s="5">
         <v>1</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I17" s="5">
         <v>10</v>
       </c>
-      <c r="J17" s="5" t="s">
-        <v>35</v>
-      </c>
     </row>
-    <row r="18" ht="28" customHeight="1" spans="2:10">
+    <row r="18" ht="28" customHeight="1" spans="2:9">
       <c r="B18" s="5">
         <v>504</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F18" s="5">
-        <v>4000</v>
+        <v>6003</v>
       </c>
       <c r="G18" s="5">
         <v>3</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I18" s="5">
         <v>10</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
